--- a/SD_rht_contracts.xlsx
+++ b/SD_rht_contracts.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Contracts" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Reconciliation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Announced not published" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Announced rounds" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Outside the RHT series" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="355">
   <si>
     <t xml:space="preserve">state</t>
   </si>
@@ -136,6 +137,15 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
+    <t xml:space="preserve">award_pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first_seen_archive</t>
+  </si>
+  <si>
     <t xml:space="preserve">SD</t>
   </si>
   <si>
@@ -178,7 +188,7 @@
     <t xml:space="preserve">NON_HOSPITAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: commercial consultancy engaged through an RFP for services; named as the grant-programme management consultant in DOH's own release. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00002, begun 2026-04-15. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: commercial consultancy engaged through an RFP for services; named as the grant-programme management consultant in DOH's own release. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00002, begun 2026-04-15. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/26RHT00002.html</t>
@@ -211,6 +221,12 @@
     <t xml:space="preserve">Provide consultant services to SD Health Link to help manage the Digital Health Modernization and Technology Grant Program.</t>
   </si>
   <si>
+    <t xml:space="preserve">RHT series - programme administration, consulting, evaluation and workforce contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28_open_sd_contract_search_RHT.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">BUSINESS CONCEPTS &amp; APPS INC</t>
   </si>
   <si>
@@ -223,7 +239,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=26RHT00003</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: commercial consultancy engaged through an RFP for services; named as a project-management contractor in DOH's own release. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00003, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: commercial consultancy engaged through an RFP for services; named as a project-management contractor in DOH's own release. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00003, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/26RHT00003.html</t>
@@ -256,7 +272,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=26RHT00004</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: Community Health Worker Collaborative of South Dakota, a nonprofit; the register truncates the name. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00004, begun 2026-05-07. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: Community Health Worker Collaborative of South Dakota, a nonprofit; the register truncates the name. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00004, begun 2026-05-07. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/26RHT00004.html</t>
@@ -289,7 +305,7 @@
     <t xml:space="preserve">HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00006, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00006, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/26RHT00006.html</t>
@@ -322,7 +338,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00001</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: South Dakota education service cooperative, a nonprofit. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00001, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: South Dakota education service cooperative, a nonprofit. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00001, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00001.html</t>
@@ -352,7 +368,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00005</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: national management consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00005, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: national management consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00005, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00005.html</t>
@@ -385,7 +401,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00007</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: actuarial and accounting firm engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00007, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: actuarial and accounting firm engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00007, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00007.html</t>
@@ -418,7 +434,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00008</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: Sioux Falls nonprofit senior services centre. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00008, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: Sioux Falls nonprofit senior services centre. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00008, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00008.html</t>
@@ -442,7 +458,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00009</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00009, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00009, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00009.html</t>
@@ -460,7 +476,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00010</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00010, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00010, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00010.html</t>
@@ -484,7 +500,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00011</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00011, begun 2026-08-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00011, begun 2026-08-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00011.html</t>
@@ -511,7 +527,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00012</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: commercial health policy consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00012, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: commercial health policy consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00012, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00012.html</t>
@@ -541,7 +557,7 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00013</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00013, begun 2026-07-17. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds, neither of which has been posted to this register.</t>
+    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00013, begun 2026-07-17. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00013.html</t>
@@ -556,6 +572,354 @@
     <t xml:space="preserve">To establish regional EMS hubs that improve coordination, resource sharing, operational efficiency, and overall system performance across South Dakota.</t>
   </si>
   <si>
+    <t xml:space="preserve">SOUTH DAKOTA DOULAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT_TYPE_INFERRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00014, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00014.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALLBACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expand and strengthen the doula workforce in South Dakota through recruitment, training, certification, and workforce development activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24_open_sd_contract_search_RHT.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD URBAN INDIAN HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBAL_ORG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | PIERRE, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a tribal entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00015, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00015.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHT series - Rural Strong grants (subset of the 28-grant, $31.5M round of 2026-07-23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSITY OF SOUTH DAKOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | Contract with State or Local Government Agency (5-18D-21(8)) | VERMILLION, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00016, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00016.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERMILLION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETE HEALTH CENTER OF BH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | RAPID CITY, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00017, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00017.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPID CITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMUNITY MEMORIAL HOSPITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOSPITAL_OR_SYSTEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | BURKE, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00018, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00018.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00019, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00019.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design, implement, host, and maintain a statewide education and training platform that expands access to high-quality, accredited training for all healthcare professionals in South Dakota, with a particular emphasis on supporting rural healthcare providers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09RHT-022 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | STURGIS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: South Dakota education service cooperative, a nonprofit. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00020, begun 2026-08-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00020.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09RHT-022 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide strategic leadership and operational support within the Office of Rural Health and Emergency Services in advancing rural healthcare transformation initiatives across the state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00021, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00021.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAULKTON AREA MEDICAL CENTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | FAULKTON, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city FAULKTON, CCN 431301, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a medical center. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00022, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00022.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAULKTON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHILIP HEALTH SERVICES INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | PHILIP, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city PHILIP, CCN 431319, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: NONPROFIT_CBO/LOW.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient typed HOSPITAL_OR_SYSTEM on an ARCHIVED FEDERAL RECORD, not on its name: the register publishes no form, and CMS's Hospital Enrollments file carries this exact string in the same city (see recipient_type_source). MEDIUM, not HIGH: the match is on CMS's enrolment file, not an AHA/POS CCN reconciliation. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00023, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00023.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEDERAL_RECORD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHILIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | REDFIELD, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): DOING BUSINESS AS NAME = the register's own string, city REDFIELD, CCN 431316, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00024, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00024.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDFIELD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENNETT COUNTY HOSPITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | MARTIN, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00025, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00025.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGINEERING SOLUTIONS INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 27-09RHT-024 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | WEST LINN, OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a technology vendor. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00026, begun 2026-09-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00026.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 27-09RHT-024 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEST LINN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide grant and administrative support for the Rural Health Transformation Project</t>
+  </si>
+  <si>
     <t xml:space="preserve">measure</t>
   </si>
   <si>
@@ -565,67 +929,91 @@
     <t xml:space="preserve">contracts extracted from the RHT series</t>
   </si>
   <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distinct vendors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total extracted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,618,367.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">largest single contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,462,802.00</t>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distinct vendor strings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total extracted (BOTH pools; never add to sd_year1_awardees.csv round totals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,223,177.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- POOL 1: ADMINISTRATIVE --</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">administrative / programme contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">administrative total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,344,025.00</t>
   </si>
   <si>
     <t xml:space="preserve">what these are</t>
   </si>
   <si>
-    <t xml:space="preserve">programme management, consulting, evaluation, workforce training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-- NOT EXTRACTED, BECAUSE NOT PUBLISHED --</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Strong round announced 2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$31,500,000 to 28 projects across 20 health systems</t>
+    <t xml:space="preserve">programme management, consulting, evaluation, workforce training, doula workforce, training platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- POOL 2: RURAL STRONG GRANTS (Tier 3) --</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Strong grant contracts on the register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 of the 28 announced 2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Strong total on the register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,879,152.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Strong round total (KB0046839)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31,500,000.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relationship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the register's contracts are INSIDE the round total; the round total already includes them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Strong grants not yet on the register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 -- NAMED NOWHERE; their amount is stated by no source and is NOT computed here (§6.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- NOT ON THE REGISTER --</t>
   </si>
   <si>
     <t xml:space="preserve">Technology/data round announced 2026-08-19</t>
   </si>
   <si>
-    <t xml:space="preserve">$90,000,000 to 82 rural healthcare organizations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">either round found on open.sd.gov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">announcements archived</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no -- they are on news.sd.gov, refused at CONNECT (403)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">announced but unextracted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121,500,000.00</t>
+    <t xml:space="preserve">$90,000,000 to 82 rural healthcare organizations -- no contract on open.sd.gov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHTP contracts OUTSIDE the RHT series (not extracted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 -- 27SC091800 SD FOUNDATION FOR MEDICAL CARE $150,000; 26SC090058 BLACK HILLS SPECIAL SERVICES $ 45,000</t>
   </si>
   <si>
     <t xml:space="preserve">CMS Year 1 award for South Dakota</t>
@@ -640,13 +1028,16 @@
     <t xml:space="preserve">rows distributed_to_hospital = Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">0</t>
+    <t xml:space="preserve">5</t>
   </si>
   <si>
     <t xml:space="preserve">dollars distributed_to_hospital = Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00</t>
+    <t xml:space="preserve">716,800.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distinct hospitals among them</t>
   </si>
   <si>
     <t xml:space="preserve">round</t>
@@ -674,6 +1065,21 @@
   </si>
   <si>
     <t xml:space="preserve">82 rural healthcare organizations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27SC091800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grant, begun 2026-05-01, CFDA 93.798; description is DOH's generic Rural Health Transformation paragraph -- RHTP money outside the series, a candidate for extraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26SC090058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contract, begun 2025-09-22 -- BEFORE the 2025-12-29 Notice of Award -- Professional Services under $50K; 'grant writing support for the Rural Health Transformation Program funding opportunity': APPLICATION support, not an award of RHTP money (§6.2 date test)</t>
   </si>
 </sst>
 </file>
@@ -1129,52 +1535,61 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D2" t="n">
         <v>1462802</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P2"/>
       <c r="Q2"/>
@@ -1182,107 +1597,114 @@
       <c r="S2"/>
       <c r="T2"/>
       <c r="U2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V2"/>
       <c r="W2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Z2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AA2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AB2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AG2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AH2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI2" s="1" t="n">
         <v>46127</v>
       </c>
       <c r="AJ2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL2" t="s">
         <v>63</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>60</v>
       </c>
       <c r="AM2"/>
       <c r="AN2" t="s">
-        <v>64</v>
+        <v>67</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP2"/>
+      <c r="AQ2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D3" t="n">
         <v>250000</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P3"/>
       <c r="Q3"/>
@@ -1290,107 +1712,114 @@
       <c r="S3"/>
       <c r="T3"/>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V3"/>
       <c r="W3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="Z3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AB3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AG3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI3" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="AJ3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AK3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AM3"/>
       <c r="AN3" t="s">
-        <v>74</v>
+        <v>79</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP3"/>
+      <c r="AQ3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D4" t="n">
         <v>399013</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P4"/>
       <c r="Q4"/>
@@ -1398,107 +1827,114 @@
       <c r="S4"/>
       <c r="T4"/>
       <c r="U4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V4"/>
       <c r="W4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AA4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AB4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AG4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AH4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI4" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="AJ4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AK4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AM4"/>
       <c r="AN4" t="s">
-        <v>84</v>
+        <v>89</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP4"/>
+      <c r="AQ4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D5" t="n">
         <v>225000</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P5"/>
       <c r="Q5"/>
@@ -1506,107 +1942,114 @@
       <c r="S5"/>
       <c r="T5"/>
       <c r="U5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V5"/>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="Z5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="AA5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="AB5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AF5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AH5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI5" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="AJ5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AM5"/>
       <c r="AN5" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP5"/>
+      <c r="AQ5" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D6" t="n">
         <v>503000</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -1614,107 +2057,114 @@
       <c r="S6"/>
       <c r="T6"/>
       <c r="U6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V6"/>
       <c r="W6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Z6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AB6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="AG6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AH6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI6" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="AJ6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="AK6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="AM6"/>
       <c r="AN6" t="s">
-        <v>107</v>
+        <v>112</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP6"/>
+      <c r="AQ6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D7" t="n">
         <v>567350</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="M7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -1722,107 +2172,114 @@
       <c r="S7"/>
       <c r="T7"/>
       <c r="U7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V7"/>
       <c r="W7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Z7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AA7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="AB7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AG7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AH7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI7" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="AJ7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AK7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AM7"/>
       <c r="AN7" t="s">
-        <v>118</v>
+        <v>123</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP7"/>
+      <c r="AQ7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D8" t="n">
         <v>450000</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -1830,107 +2287,114 @@
       <c r="S8"/>
       <c r="T8"/>
       <c r="U8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V8"/>
       <c r="W8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="Z8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AA8" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AB8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF8" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AH8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI8" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="AJ8" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="AK8" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="AL8" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AM8"/>
       <c r="AN8" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP8"/>
+      <c r="AQ8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D9" t="n">
         <v>226930</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K9" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -1938,105 +2402,112 @@
       <c r="S9"/>
       <c r="T9"/>
       <c r="U9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V9"/>
       <c r="W9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y9" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="Z9" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AA9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AB9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF9"/>
       <c r="AG9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AH9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI9" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AK9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL9"/>
       <c r="AM9" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AN9" t="s">
-        <v>138</v>
+        <v>143</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP9"/>
+      <c r="AQ9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
         <v>130571</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K10" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -2044,105 +2515,112 @@
       <c r="S10"/>
       <c r="T10"/>
       <c r="U10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V10"/>
       <c r="W10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="Z10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AA10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="AB10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF10"/>
       <c r="AG10" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AH10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI10" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AK10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL10"/>
       <c r="AM10" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AN10" t="s">
-        <v>145</v>
+        <v>150</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP10"/>
+      <c r="AQ10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
         <v>170816</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K11" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -2150,105 +2628,112 @@
       <c r="S11"/>
       <c r="T11"/>
       <c r="U11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V11"/>
       <c r="W11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y11" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Z11" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AA11" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AB11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF11"/>
       <c r="AG11" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AH11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AK11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL11"/>
       <c r="AM11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AN11" t="s">
-        <v>151</v>
+        <v>156</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP11"/>
+      <c r="AQ11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B12" t="n">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>88800</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -2256,107 +2741,114 @@
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V12"/>
       <c r="W12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Z12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE12" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AF12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AH12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI12" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AK12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AM12"/>
       <c r="AN12" t="s">
-        <v>160</v>
+        <v>165</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP12"/>
+      <c r="AQ12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D13" t="n">
         <v>425000</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -2364,107 +2856,114 @@
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V13"/>
       <c r="W13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y13" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="Z13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AA13" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AB13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF13" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AG13" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="AH13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI13" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="AJ13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AK13" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AM13"/>
       <c r="AN13" t="s">
-        <v>171</v>
+        <v>176</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP13"/>
+      <c r="AQ13" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B14" t="n">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
         <v>719085</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K14" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L14" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -2472,60 +2971,1578 @@
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V14"/>
       <c r="W14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="X14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y14" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Z14" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AA14" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AB14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AD14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AF14" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AG14" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="AH14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI14" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="AJ14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AK14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AL14" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM14"/>
       <c r="AN14" t="s">
-        <v>179</v>
+        <v>184</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP14"/>
+      <c r="AQ14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133352</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" t="s">
+        <v>187</v>
+      </c>
+      <c r="M15" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" t="s">
+        <v>53</v>
+      </c>
+      <c r="O15" t="s">
+        <v>54</v>
+      </c>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15" t="s">
+        <v>188</v>
+      </c>
+      <c r="V15" t="s">
+        <v>189</v>
+      </c>
+      <c r="W15" t="s">
+        <v>56</v>
+      </c>
+      <c r="X15" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF15"/>
+      <c r="AG15" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL15"/>
+      <c r="AM15" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>194</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP15"/>
+      <c r="AQ15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" t="n">
+        <v>467790</v>
+      </c>
+      <c r="E16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" t="s">
+        <v>199</v>
+      </c>
+      <c r="L16" t="s">
+        <v>200</v>
+      </c>
+      <c r="M16" t="s">
+        <v>52</v>
+      </c>
+      <c r="N16" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" t="s">
+        <v>54</v>
+      </c>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16" t="s">
+        <v>95</v>
+      </c>
+      <c r="V16"/>
+      <c r="W16" t="s">
+        <v>56</v>
+      </c>
+      <c r="X16" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF16"/>
+      <c r="AG16" t="s">
+        <v>203</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL16"/>
+      <c r="AM16" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" t="n">
+        <v>324000</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" t="s">
+        <v>208</v>
+      </c>
+      <c r="H17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" t="s">
+        <v>209</v>
+      </c>
+      <c r="L17" t="s">
+        <v>210</v>
+      </c>
+      <c r="M17" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17" t="s">
+        <v>53</v>
+      </c>
+      <c r="O17" t="s">
+        <v>54</v>
+      </c>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17" t="s">
+        <v>95</v>
+      </c>
+      <c r="V17"/>
+      <c r="W17" t="s">
+        <v>56</v>
+      </c>
+      <c r="X17" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>213</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI17" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM17"/>
+      <c r="AN17" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" t="n">
+        <v>370562</v>
+      </c>
+      <c r="E18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
+        <v>216</v>
+      </c>
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" t="s">
+        <v>217</v>
+      </c>
+      <c r="L18" t="s">
+        <v>218</v>
+      </c>
+      <c r="M18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N18" t="s">
+        <v>53</v>
+      </c>
+      <c r="O18" t="s">
+        <v>54</v>
+      </c>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18" t="s">
+        <v>188</v>
+      </c>
+      <c r="V18" t="s">
+        <v>189</v>
+      </c>
+      <c r="W18" t="s">
+        <v>56</v>
+      </c>
+      <c r="X18" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF18"/>
+      <c r="AG18" t="s">
+        <v>221</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI18" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>222</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL18"/>
+      <c r="AM18" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D19" t="n">
+        <v>145500</v>
+      </c>
+      <c r="E19" t="s">
+        <v>224</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" t="s">
+        <v>225</v>
+      </c>
+      <c r="H19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" t="s">
+        <v>226</v>
+      </c>
+      <c r="L19" t="s">
+        <v>227</v>
+      </c>
+      <c r="M19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" t="s">
+        <v>53</v>
+      </c>
+      <c r="O19" t="s">
+        <v>54</v>
+      </c>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19" t="s">
+        <v>95</v>
+      </c>
+      <c r="V19"/>
+      <c r="W19" t="s">
+        <v>228</v>
+      </c>
+      <c r="X19" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF19"/>
+      <c r="AG19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI19" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL19"/>
+      <c r="AM19" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" t="n">
+        <v>307228</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
+        <v>208</v>
+      </c>
+      <c r="H20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" t="s">
+        <v>233</v>
+      </c>
+      <c r="L20" t="s">
+        <v>234</v>
+      </c>
+      <c r="M20" t="s">
+        <v>52</v>
+      </c>
+      <c r="N20" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20" t="s">
+        <v>54</v>
+      </c>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20" t="s">
+        <v>95</v>
+      </c>
+      <c r="V20"/>
+      <c r="W20" t="s">
+        <v>56</v>
+      </c>
+      <c r="X20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>234</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>237</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI20" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM20"/>
+      <c r="AN20" t="s">
+        <v>238</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP20"/>
+      <c r="AQ20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="n">
+        <v>449402</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
+        <v>239</v>
+      </c>
+      <c r="H21" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" t="s">
+        <v>240</v>
+      </c>
+      <c r="L21" t="s">
+        <v>241</v>
+      </c>
+      <c r="M21" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21" t="s">
+        <v>53</v>
+      </c>
+      <c r="O21" t="s">
+        <v>54</v>
+      </c>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21" t="s">
+        <v>55</v>
+      </c>
+      <c r="V21"/>
+      <c r="W21" t="s">
+        <v>56</v>
+      </c>
+      <c r="X21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>244</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>245</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI21" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>244</v>
+      </c>
+      <c r="AM21"/>
+      <c r="AN21" t="s">
+        <v>246</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP21"/>
+      <c r="AQ21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" t="n">
+        <v>185676</v>
+      </c>
+      <c r="E22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" t="s">
+        <v>48</v>
+      </c>
+      <c r="I22" t="s">
+        <v>48</v>
+      </c>
+      <c r="J22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" t="s">
+        <v>247</v>
+      </c>
+      <c r="L22" t="s">
+        <v>248</v>
+      </c>
+      <c r="M22" t="s">
+        <v>52</v>
+      </c>
+      <c r="N22" t="s">
+        <v>53</v>
+      </c>
+      <c r="O22" t="s">
+        <v>54</v>
+      </c>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22" t="s">
+        <v>95</v>
+      </c>
+      <c r="V22"/>
+      <c r="W22" t="s">
+        <v>56</v>
+      </c>
+      <c r="X22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>251</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI22" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM22"/>
+      <c r="AN22" t="s">
+        <v>238</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP22"/>
+      <c r="AQ22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>252</v>
+      </c>
+      <c r="D23" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E23" t="s">
+        <v>224</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" t="s">
+        <v>253</v>
+      </c>
+      <c r="H23" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" t="s">
+        <v>254</v>
+      </c>
+      <c r="L23" t="s">
+        <v>255</v>
+      </c>
+      <c r="M23" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" t="s">
+        <v>53</v>
+      </c>
+      <c r="O23" t="s">
+        <v>54</v>
+      </c>
+      <c r="P23" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23" t="s">
+        <v>257</v>
+      </c>
+      <c r="U23" t="s">
+        <v>95</v>
+      </c>
+      <c r="V23"/>
+      <c r="W23" t="s">
+        <v>228</v>
+      </c>
+      <c r="X23" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF23"/>
+      <c r="AG23" t="s">
+        <v>260</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI23" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>261</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL23"/>
+      <c r="AM23" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>262</v>
+      </c>
+      <c r="D24" t="n">
+        <v>181600</v>
+      </c>
+      <c r="E24" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" t="s">
+        <v>263</v>
+      </c>
+      <c r="H24" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" t="s">
+        <v>264</v>
+      </c>
+      <c r="L24" t="s">
+        <v>265</v>
+      </c>
+      <c r="M24" t="s">
+        <v>52</v>
+      </c>
+      <c r="N24" t="s">
+        <v>53</v>
+      </c>
+      <c r="O24" t="s">
+        <v>54</v>
+      </c>
+      <c r="P24" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24" t="s">
+        <v>267</v>
+      </c>
+      <c r="U24" t="s">
+        <v>55</v>
+      </c>
+      <c r="V24"/>
+      <c r="W24" t="s">
+        <v>228</v>
+      </c>
+      <c r="X24" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>270</v>
+      </c>
+      <c r="AF24"/>
+      <c r="AG24" t="s">
+        <v>271</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI24" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>272</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL24"/>
+      <c r="AM24" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" t="n">
+        <v>103700</v>
+      </c>
+      <c r="E25" t="s">
+        <v>224</v>
+      </c>
+      <c r="F25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" t="s">
+        <v>273</v>
+      </c>
+      <c r="H25" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" t="s">
+        <v>274</v>
+      </c>
+      <c r="L25" t="s">
+        <v>275</v>
+      </c>
+      <c r="M25" t="s">
+        <v>52</v>
+      </c>
+      <c r="N25" t="s">
+        <v>53</v>
+      </c>
+      <c r="O25" t="s">
+        <v>54</v>
+      </c>
+      <c r="P25" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25" t="s">
+        <v>277</v>
+      </c>
+      <c r="U25" t="s">
+        <v>95</v>
+      </c>
+      <c r="V25"/>
+      <c r="W25" t="s">
+        <v>228</v>
+      </c>
+      <c r="X25" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>278</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>279</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF25"/>
+      <c r="AG25" t="s">
+        <v>280</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI25" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL25"/>
+      <c r="AM25" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>282</v>
+      </c>
+      <c r="D26" t="n">
+        <v>248000</v>
+      </c>
+      <c r="E26" t="s">
+        <v>224</v>
+      </c>
+      <c r="F26" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" t="s">
+        <v>283</v>
+      </c>
+      <c r="H26" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" t="s">
+        <v>284</v>
+      </c>
+      <c r="L26" t="s">
+        <v>285</v>
+      </c>
+      <c r="M26" t="s">
+        <v>52</v>
+      </c>
+      <c r="N26" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26" t="s">
+        <v>54</v>
+      </c>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26" t="s">
+        <v>95</v>
+      </c>
+      <c r="V26"/>
+      <c r="W26" t="s">
+        <v>228</v>
+      </c>
+      <c r="X26" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>287</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF26"/>
+      <c r="AG26" t="s">
+        <v>288</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI26" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>289</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL26"/>
+      <c r="AM26" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" t="n">
+        <v>650000</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
+        <v>291</v>
+      </c>
+      <c r="H27" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" t="s">
+        <v>292</v>
+      </c>
+      <c r="L27" t="s">
+        <v>293</v>
+      </c>
+      <c r="M27" t="s">
+        <v>52</v>
+      </c>
+      <c r="N27" t="s">
+        <v>53</v>
+      </c>
+      <c r="O27" t="s">
+        <v>54</v>
+      </c>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27" t="s">
+        <v>55</v>
+      </c>
+      <c r="V27"/>
+      <c r="W27" t="s">
+        <v>56</v>
+      </c>
+      <c r="X27" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>296</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>297</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI27" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>298</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>299</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>296</v>
+      </c>
+      <c r="AM27"/>
+      <c r="AN27" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP27"/>
+      <c r="AQ27" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2541,130 +4558,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>180</v>
+        <v>301</v>
       </c>
       <c r="B1" t="s">
-        <v>181</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>305</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>186</v>
+        <v>307</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>317</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>318</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>322</v>
       </c>
       <c r="B12" t="s">
-        <v>203</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>324</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>326</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>328</v>
       </c>
       <c r="B15" t="s">
-        <v>208</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>209</v>
+        <v>329</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B17" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B18" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>335</v>
+      </c>
+      <c r="B19" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>336</v>
+      </c>
+      <c r="B20" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>338</v>
+      </c>
+      <c r="B21" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>340</v>
+      </c>
+      <c r="B22" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -2680,13 +4745,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>341</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="C1" t="s">
-        <v>213</v>
+        <v>343</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -2694,13 +4759,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>344</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>345</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>346</v>
       </c>
       <c r="D2" t="n">
         <v>31500000</v>
@@ -2708,16 +4773,69 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>217</v>
+        <v>347</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>348</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>349</v>
       </c>
       <c r="D3" t="n">
         <v>90000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D3" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/SD_rht_contracts.xlsx
+++ b/SD_rht_contracts.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
   <si>
     <t xml:space="preserve">state</t>
   </si>
@@ -920,6 +920,360 @@
     <t xml:space="preserve">Provide grant and administrative support for the Rural Health Transformation Project</t>
   </si>
   <si>
+    <t xml:space="preserve">HURON REGIONAL MEDICAL CENTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | HURON, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a medical center. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00028, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00028.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HURON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02_open_sd_contract_search_RHT.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMUNITY HEALTHCARE ASSOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00029, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00029.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWDLE HOSPITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | BOWDLE, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city BOWDLE, CCN 431318, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00030, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00030.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANFORD HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00031, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00031.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOBRIDGE REGIONAL HOSPITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | MOBRIDGE, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city MOBRIDGE, CCN 431325, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00032, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00032.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOBRIDGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALL RIVER HEALTH SERVICES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | HOT SPRINGS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city HOT SPRINGS, CCN 431322, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: NONPROFIT_CBO/LOW.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient typed HOSPITAL_OR_SYSTEM on an ARCHIVED FEDERAL RECORD, not on its name: the register publishes no form, and CMS's Hospital Enrollments file carries this exact string in the same city (see recipient_type_source). MEDIUM, not HIGH: the match is on CMS's enrolment file, not an AHA/POS CCN reconciliation. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00033, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00033.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOT SPRINGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVERA HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00034, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00034.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a medical center. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00035, begun 2026-07-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Faulkton Area Medical Center: 'implement chronic disease management activities'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00035.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose of this contract is to implement chronic disease management activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHT series - named RHTP awards whose round the register does not state (may sit INSIDE the $90M Technology and data round; NEVER added to it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNPLACED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00036, begun 2026-07-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Mobridge Regional Hospital: 'implement chronic disease management activities'. No round named; Mobridge's Rural Strong grant is a SEPARATE contract (27RHT00032).). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00036.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HURON CLINIC FOUNDATION LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00037, begun 2026-07-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Huron Clinic Foundation: 'fund equipment for clinical operations'. Reads like the $90M round's 'digital equipment upgrades'; the register does not say so.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00037.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is to fund equipment for clinical operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVERA MCKENNAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | MILBANK, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city MILBANK, CCN 431326, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: NONPROFIT_CBO/LOW.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient typed HOSPITAL_OR_SYSTEM on an ARCHIVED FEDERAL RECORD, not on its name: the register publishes no form, and CMS's Hospital Enrollments file carries this exact string in the same city (see recipient_type_source). MEDIUM, not HIGH: the match is on CMS's enrolment file, not an AHA/POS CCN reconciliation. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00038, begun 2026-08-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Avera McKennan (Milbank): 'implement the Avera Maternal Health Hub &amp; eOB Network'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00038.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILBANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To implement the Avera Maternal Health Hub &amp; eOB Network as part of the Rural Health Transformation Project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAKOTA STATE UNIVERSITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | Contract with State or Local Government Agency (5-18D-21(8)) | MADISON, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00039, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Dakota State University: 'Rural Healthcare Cybersecurity &amp; Digital Regional Innovation Center'. KB0047023 names Regional Innovation Centers; the register, a contract with a state agency begun 2026-02-20, does not name the round.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00039.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MADISON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The DSU Rural Healthcare Cybersecurity &amp; Digital Regional Innovation Center will strengthen cybersecurity readiness, EHR implementation, and digital technical assistance for rural and underserved healthcare organizations across South Dakota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVERA AT HOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00040, begun 2026-07-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Avera at Home: 'implement chronic disease management activities'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00040.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLACK HILLS WORKS INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00041, begun 2026-02-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Black Hills Works: 'fund network infrastructure upgrades', begun 2026-02-01. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00041.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is to fund network infrastructure upgrades.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATE VETERANS HOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | Contract with State or Local Government Agency (5-18D-21(8)) | HOT SPRINGS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00047, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: State Veterans Home: 'Technical Assistance and Support to assist with their EHR planning'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00047.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is to provide contractual Technical Assistance and Support to assist with their EHR planning.</t>
+  </si>
+  <si>
     <t xml:space="preserve">measure</t>
   </si>
   <si>
@@ -929,19 +1283,19 @@
     <t xml:space="preserve">contracts extracted from the RHT series</t>
   </si>
   <si>
-    <t xml:space="preserve">26</t>
+    <t xml:space="preserve">41</t>
   </si>
   <si>
     <t xml:space="preserve">distinct vendor strings</t>
   </si>
   <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total extracted (BOTH pools; never add to sd_year1_awardees.csv round totals)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,223,177.00</t>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total extracted (ALL THREE pools; never add to sd_year1_awardees.csv round totals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26,836,144.00</t>
   </si>
   <si>
     <t xml:space="preserve">-- POOL 1: ADMINISTRATIVE --</t>
@@ -953,13 +1307,13 @@
     <t xml:space="preserve">administrative / programme contracts</t>
   </si>
   <si>
-    <t xml:space="preserve">18</t>
+    <t xml:space="preserve">19</t>
   </si>
   <si>
     <t xml:space="preserve">administrative total</t>
   </si>
   <si>
-    <t xml:space="preserve">7,344,025.00</t>
+    <t xml:space="preserve">7,693,072.00</t>
   </si>
   <si>
     <t xml:space="preserve">what these are</t>
@@ -974,13 +1328,13 @@
     <t xml:space="preserve">Rural Strong grant contracts on the register</t>
   </si>
   <si>
-    <t xml:space="preserve">8 of the 28 announced 2026-07-23</t>
+    <t xml:space="preserve">14 of the 28 announced 2026-07-23</t>
   </si>
   <si>
     <t xml:space="preserve">Rural Strong total on the register</t>
   </si>
   <si>
-    <t xml:space="preserve">1,879,152.00</t>
+    <t xml:space="preserve">15,967,960.00</t>
   </si>
   <si>
     <t xml:space="preserve">Rural Strong round total (KB0046839)</t>
@@ -998,16 +1352,43 @@
     <t xml:space="preserve">Rural Strong grants not yet on the register</t>
   </si>
   <si>
-    <t xml:space="preserve">20 -- NAMED NOWHERE; their amount is stated by no source and is NOT computed here (§6.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-- NOT ON THE REGISTER --</t>
+    <t xml:space="preserve">14 -- NAMED NOWHERE; their amount is stated by no source and is NOT computed here (§6.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- POOL 3: NAMED AWARDS, ROUND NOT STATED (Tier 3) --</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unplaced award contracts on the register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unplaced total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,175,112.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relationship to the rounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the register names no round; they MAY sit inside the $90M Technology and data round and are NEVER added to it; capped at its 82 grants / $90M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- ANNOUNCED ROUNDS --</t>
   </si>
   <si>
     <t xml:space="preserve">Technology/data round announced 2026-08-19</t>
   </si>
   <si>
-    <t xml:space="preserve">$90,000,000 to 82 rural healthcare organizations -- no contract on open.sd.gov</t>
+    <t xml:space="preserve">$90,000,000 to 82 rural healthcare organizations -- NO contract on open.sd.gov names this round; 8 unplaced contracts ($3,175,112.00) may be among them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Strong + unplaced, against the $121,500,000 announced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,143,072.00 -- inside, never on top</t>
   </si>
   <si>
     <t xml:space="preserve">RHTP contracts OUTSIDE the RHT series (not extracted)</t>
@@ -1028,16 +1409,19 @@
     <t xml:space="preserve">rows distributed_to_hospital = Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
+    <t xml:space="preserve">12</t>
   </si>
   <si>
     <t xml:space="preserve">dollars distributed_to_hospital = Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">716,800.00</t>
+    <t xml:space="preserve">9,636,252.00</t>
   </si>
   <si>
     <t xml:space="preserve">distinct hospitals among them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
   </si>
   <si>
     <t xml:space="preserve">round</t>
@@ -4545,6 +4929,1771 @@
         <v>195</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1258349</v>
+      </c>
+      <c r="E28" t="s">
+        <v>224</v>
+      </c>
+      <c r="F28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" t="s">
+        <v>302</v>
+      </c>
+      <c r="H28" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" t="s">
+        <v>303</v>
+      </c>
+      <c r="L28" t="s">
+        <v>304</v>
+      </c>
+      <c r="M28" t="s">
+        <v>52</v>
+      </c>
+      <c r="N28" t="s">
+        <v>53</v>
+      </c>
+      <c r="O28" t="s">
+        <v>54</v>
+      </c>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28" t="s">
+        <v>95</v>
+      </c>
+      <c r="V28"/>
+      <c r="W28" t="s">
+        <v>228</v>
+      </c>
+      <c r="X28" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>305</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF28"/>
+      <c r="AG28" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI28" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>308</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL28"/>
+      <c r="AM28" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>310</v>
+      </c>
+      <c r="D29" t="n">
+        <v>349047</v>
+      </c>
+      <c r="E29" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" t="s">
+        <v>48</v>
+      </c>
+      <c r="I29" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" t="s">
+        <v>311</v>
+      </c>
+      <c r="L29" t="s">
+        <v>312</v>
+      </c>
+      <c r="M29" t="s">
+        <v>52</v>
+      </c>
+      <c r="N29" t="s">
+        <v>53</v>
+      </c>
+      <c r="O29" t="s">
+        <v>54</v>
+      </c>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29" t="s">
+        <v>188</v>
+      </c>
+      <c r="V29" t="s">
+        <v>189</v>
+      </c>
+      <c r="W29" t="s">
+        <v>56</v>
+      </c>
+      <c r="X29" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>313</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>314</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF29"/>
+      <c r="AG29" t="s">
+        <v>315</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI29" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL29"/>
+      <c r="AM29" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>238</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP29"/>
+      <c r="AQ29" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>316</v>
+      </c>
+      <c r="D30" t="n">
+        <v>418563</v>
+      </c>
+      <c r="E30" t="s">
+        <v>224</v>
+      </c>
+      <c r="F30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" t="s">
+        <v>317</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" t="s">
+        <v>48</v>
+      </c>
+      <c r="J30" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" t="s">
+        <v>318</v>
+      </c>
+      <c r="L30" t="s">
+        <v>319</v>
+      </c>
+      <c r="M30" t="s">
+        <v>52</v>
+      </c>
+      <c r="N30" t="s">
+        <v>53</v>
+      </c>
+      <c r="O30" t="s">
+        <v>54</v>
+      </c>
+      <c r="P30" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30" t="s">
+        <v>321</v>
+      </c>
+      <c r="U30" t="s">
+        <v>95</v>
+      </c>
+      <c r="V30"/>
+      <c r="W30" t="s">
+        <v>228</v>
+      </c>
+      <c r="X30" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>322</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF30"/>
+      <c r="AG30" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI30" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>325</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL30"/>
+      <c r="AM30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>326</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5442000</v>
+      </c>
+      <c r="E31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
+        <v>136</v>
+      </c>
+      <c r="H31" t="s">
+        <v>48</v>
+      </c>
+      <c r="I31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" t="s">
+        <v>49</v>
+      </c>
+      <c r="K31" t="s">
+        <v>327</v>
+      </c>
+      <c r="L31" t="s">
+        <v>328</v>
+      </c>
+      <c r="M31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N31" t="s">
+        <v>53</v>
+      </c>
+      <c r="O31" t="s">
+        <v>54</v>
+      </c>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31" t="s">
+        <v>188</v>
+      </c>
+      <c r="V31" t="s">
+        <v>189</v>
+      </c>
+      <c r="W31" t="s">
+        <v>56</v>
+      </c>
+      <c r="X31" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>330</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF31"/>
+      <c r="AG31" t="s">
+        <v>331</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI31" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL31"/>
+      <c r="AM31" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP31" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>332</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2704989</v>
+      </c>
+      <c r="E32" t="s">
+        <v>224</v>
+      </c>
+      <c r="F32" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" t="s">
+        <v>333</v>
+      </c>
+      <c r="H32" t="s">
+        <v>48</v>
+      </c>
+      <c r="I32" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" t="s">
+        <v>334</v>
+      </c>
+      <c r="L32" t="s">
+        <v>335</v>
+      </c>
+      <c r="M32" t="s">
+        <v>52</v>
+      </c>
+      <c r="N32" t="s">
+        <v>53</v>
+      </c>
+      <c r="O32" t="s">
+        <v>54</v>
+      </c>
+      <c r="P32" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q32"/>
+      <c r="R32"/>
+      <c r="S32"/>
+      <c r="T32" t="s">
+        <v>337</v>
+      </c>
+      <c r="U32" t="s">
+        <v>95</v>
+      </c>
+      <c r="V32"/>
+      <c r="W32" t="s">
+        <v>228</v>
+      </c>
+      <c r="X32" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>339</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>335</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF32"/>
+      <c r="AG32" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI32" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>341</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL32"/>
+      <c r="AM32" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP32" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>342</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2699907</v>
+      </c>
+      <c r="E33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F33" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" t="s">
+        <v>343</v>
+      </c>
+      <c r="H33" t="s">
+        <v>48</v>
+      </c>
+      <c r="I33" t="s">
+        <v>48</v>
+      </c>
+      <c r="J33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" t="s">
+        <v>344</v>
+      </c>
+      <c r="L33" t="s">
+        <v>345</v>
+      </c>
+      <c r="M33" t="s">
+        <v>52</v>
+      </c>
+      <c r="N33" t="s">
+        <v>53</v>
+      </c>
+      <c r="O33" t="s">
+        <v>54</v>
+      </c>
+      <c r="P33" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q33"/>
+      <c r="R33"/>
+      <c r="S33"/>
+      <c r="T33" t="s">
+        <v>347</v>
+      </c>
+      <c r="U33" t="s">
+        <v>55</v>
+      </c>
+      <c r="V33"/>
+      <c r="W33" t="s">
+        <v>228</v>
+      </c>
+      <c r="X33" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>348</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>349</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>270</v>
+      </c>
+      <c r="AF33"/>
+      <c r="AG33" t="s">
+        <v>350</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI33" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>351</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL33"/>
+      <c r="AM33" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>352</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1565000</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" t="s">
+        <v>48</v>
+      </c>
+      <c r="I34" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K34" t="s">
+        <v>353</v>
+      </c>
+      <c r="L34" t="s">
+        <v>354</v>
+      </c>
+      <c r="M34" t="s">
+        <v>52</v>
+      </c>
+      <c r="N34" t="s">
+        <v>53</v>
+      </c>
+      <c r="O34" t="s">
+        <v>54</v>
+      </c>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34" t="s">
+        <v>188</v>
+      </c>
+      <c r="V34" t="s">
+        <v>189</v>
+      </c>
+      <c r="W34" t="s">
+        <v>56</v>
+      </c>
+      <c r="X34" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>355</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>356</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>354</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF34"/>
+      <c r="AG34" t="s">
+        <v>357</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI34" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL34"/>
+      <c r="AM34" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ34" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" t="n">
+        <v>77432</v>
+      </c>
+      <c r="E35" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35" t="s">
+        <v>253</v>
+      </c>
+      <c r="H35" t="s">
+        <v>48</v>
+      </c>
+      <c r="I35" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" t="s">
+        <v>358</v>
+      </c>
+      <c r="L35" t="s">
+        <v>359</v>
+      </c>
+      <c r="M35" t="s">
+        <v>52</v>
+      </c>
+      <c r="N35" t="s">
+        <v>53</v>
+      </c>
+      <c r="O35" t="s">
+        <v>54</v>
+      </c>
+      <c r="P35" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q35"/>
+      <c r="R35"/>
+      <c r="S35"/>
+      <c r="T35" t="s">
+        <v>257</v>
+      </c>
+      <c r="U35" t="s">
+        <v>95</v>
+      </c>
+      <c r="V35"/>
+      <c r="W35" t="s">
+        <v>228</v>
+      </c>
+      <c r="X35" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>360</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>361</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF35"/>
+      <c r="AG35" t="s">
+        <v>362</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI35" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>261</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL35"/>
+      <c r="AM35" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>363</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ35" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>332</v>
+      </c>
+      <c r="D36" t="n">
+        <v>175000</v>
+      </c>
+      <c r="E36" t="s">
+        <v>224</v>
+      </c>
+      <c r="F36" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" t="s">
+        <v>333</v>
+      </c>
+      <c r="H36" t="s">
+        <v>48</v>
+      </c>
+      <c r="I36" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" t="s">
+        <v>366</v>
+      </c>
+      <c r="L36" t="s">
+        <v>367</v>
+      </c>
+      <c r="M36" t="s">
+        <v>52</v>
+      </c>
+      <c r="N36" t="s">
+        <v>53</v>
+      </c>
+      <c r="O36" t="s">
+        <v>54</v>
+      </c>
+      <c r="P36" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q36"/>
+      <c r="R36"/>
+      <c r="S36"/>
+      <c r="T36" t="s">
+        <v>337</v>
+      </c>
+      <c r="U36" t="s">
+        <v>95</v>
+      </c>
+      <c r="V36"/>
+      <c r="W36" t="s">
+        <v>228</v>
+      </c>
+      <c r="X36" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>368</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF36"/>
+      <c r="AG36" t="s">
+        <v>370</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI36" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>341</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL36"/>
+      <c r="AM36" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>363</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>371</v>
+      </c>
+      <c r="D37" t="n">
+        <v>80431</v>
+      </c>
+      <c r="E37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" t="s">
+        <v>302</v>
+      </c>
+      <c r="H37" t="s">
+        <v>48</v>
+      </c>
+      <c r="I37" t="s">
+        <v>48</v>
+      </c>
+      <c r="J37" t="s">
+        <v>49</v>
+      </c>
+      <c r="K37" t="s">
+        <v>372</v>
+      </c>
+      <c r="L37" t="s">
+        <v>373</v>
+      </c>
+      <c r="M37" t="s">
+        <v>52</v>
+      </c>
+      <c r="N37" t="s">
+        <v>53</v>
+      </c>
+      <c r="O37" t="s">
+        <v>54</v>
+      </c>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37" t="s">
+        <v>188</v>
+      </c>
+      <c r="V37" t="s">
+        <v>189</v>
+      </c>
+      <c r="W37" t="s">
+        <v>56</v>
+      </c>
+      <c r="X37" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF37"/>
+      <c r="AG37" t="s">
+        <v>376</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI37" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>308</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL37"/>
+      <c r="AM37" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>377</v>
+      </c>
+      <c r="AO37" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>378</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1585212</v>
+      </c>
+      <c r="E38" t="s">
+        <v>224</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38" t="s">
+        <v>379</v>
+      </c>
+      <c r="H38" t="s">
+        <v>48</v>
+      </c>
+      <c r="I38" t="s">
+        <v>48</v>
+      </c>
+      <c r="J38" t="s">
+        <v>49</v>
+      </c>
+      <c r="K38" t="s">
+        <v>380</v>
+      </c>
+      <c r="L38" t="s">
+        <v>381</v>
+      </c>
+      <c r="M38" t="s">
+        <v>52</v>
+      </c>
+      <c r="N38" t="s">
+        <v>53</v>
+      </c>
+      <c r="O38" t="s">
+        <v>54</v>
+      </c>
+      <c r="P38" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38"/>
+      <c r="T38" t="s">
+        <v>383</v>
+      </c>
+      <c r="U38" t="s">
+        <v>55</v>
+      </c>
+      <c r="V38"/>
+      <c r="W38" t="s">
+        <v>228</v>
+      </c>
+      <c r="X38" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>384</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>385</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>381</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>270</v>
+      </c>
+      <c r="AF38"/>
+      <c r="AG38" t="s">
+        <v>386</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI38" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>387</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL38"/>
+      <c r="AM38" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>388</v>
+      </c>
+      <c r="AO38" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP38" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ38" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>389</v>
+      </c>
+      <c r="D39" t="n">
+        <v>999242</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" t="s">
+        <v>390</v>
+      </c>
+      <c r="H39" t="s">
+        <v>48</v>
+      </c>
+      <c r="I39" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" t="s">
+        <v>391</v>
+      </c>
+      <c r="L39" t="s">
+        <v>392</v>
+      </c>
+      <c r="M39" t="s">
+        <v>52</v>
+      </c>
+      <c r="N39" t="s">
+        <v>53</v>
+      </c>
+      <c r="O39" t="s">
+        <v>54</v>
+      </c>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39" t="s">
+        <v>95</v>
+      </c>
+      <c r="V39"/>
+      <c r="W39" t="s">
+        <v>56</v>
+      </c>
+      <c r="X39" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>393</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>394</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>392</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>395</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI39" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>396</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM39"/>
+      <c r="AN39" t="s">
+        <v>397</v>
+      </c>
+      <c r="AO39" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ39" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>398</v>
+      </c>
+      <c r="D40" t="n">
+        <v>175000</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" t="s">
+        <v>46</v>
+      </c>
+      <c r="G40" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40" t="s">
+        <v>48</v>
+      </c>
+      <c r="I40" t="s">
+        <v>48</v>
+      </c>
+      <c r="J40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K40" t="s">
+        <v>399</v>
+      </c>
+      <c r="L40" t="s">
+        <v>400</v>
+      </c>
+      <c r="M40" t="s">
+        <v>52</v>
+      </c>
+      <c r="N40" t="s">
+        <v>53</v>
+      </c>
+      <c r="O40" t="s">
+        <v>54</v>
+      </c>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40"/>
+      <c r="U40" t="s">
+        <v>188</v>
+      </c>
+      <c r="V40" t="s">
+        <v>189</v>
+      </c>
+      <c r="W40" t="s">
+        <v>56</v>
+      </c>
+      <c r="X40" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>401</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>400</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF40"/>
+      <c r="AG40" t="s">
+        <v>403</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI40" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL40"/>
+      <c r="AM40" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>363</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ40" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>404</v>
+      </c>
+      <c r="D41" t="n">
+        <v>62795</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G41" t="s">
+        <v>216</v>
+      </c>
+      <c r="H41" t="s">
+        <v>48</v>
+      </c>
+      <c r="I41" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" t="s">
+        <v>49</v>
+      </c>
+      <c r="K41" t="s">
+        <v>405</v>
+      </c>
+      <c r="L41" t="s">
+        <v>406</v>
+      </c>
+      <c r="M41" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41" t="s">
+        <v>53</v>
+      </c>
+      <c r="O41" t="s">
+        <v>54</v>
+      </c>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41"/>
+      <c r="U41" t="s">
+        <v>188</v>
+      </c>
+      <c r="V41" t="s">
+        <v>189</v>
+      </c>
+      <c r="W41" t="s">
+        <v>56</v>
+      </c>
+      <c r="X41" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>407</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>408</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>406</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF41"/>
+      <c r="AG41" t="s">
+        <v>409</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI41" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>222</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL41"/>
+      <c r="AM41" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>410</v>
+      </c>
+      <c r="AO41" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP41" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ41" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
+        <v>411</v>
+      </c>
+      <c r="D42" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" t="s">
+        <v>412</v>
+      </c>
+      <c r="H42" t="s">
+        <v>48</v>
+      </c>
+      <c r="I42" t="s">
+        <v>48</v>
+      </c>
+      <c r="J42" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" t="s">
+        <v>413</v>
+      </c>
+      <c r="L42" t="s">
+        <v>414</v>
+      </c>
+      <c r="M42" t="s">
+        <v>52</v>
+      </c>
+      <c r="N42" t="s">
+        <v>53</v>
+      </c>
+      <c r="O42" t="s">
+        <v>54</v>
+      </c>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42"/>
+      <c r="U42" t="s">
+        <v>188</v>
+      </c>
+      <c r="V42" t="s">
+        <v>189</v>
+      </c>
+      <c r="W42" t="s">
+        <v>56</v>
+      </c>
+      <c r="X42" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>415</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>416</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>417</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI42" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>351</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM42"/>
+      <c r="AN42" t="s">
+        <v>418</v>
+      </c>
+      <c r="AO42" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ42" t="s">
+        <v>309</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -4558,178 +6707,218 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>301</v>
+        <v>419</v>
       </c>
       <c r="B1" t="s">
-        <v>302</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>421</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>423</v>
       </c>
       <c r="B3" t="s">
-        <v>306</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>307</v>
+        <v>425</v>
       </c>
       <c r="B4" t="s">
-        <v>308</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>309</v>
+        <v>427</v>
       </c>
       <c r="B5" t="s">
-        <v>310</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>431</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>433</v>
       </c>
       <c r="B8" t="s">
-        <v>316</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>317</v>
+        <v>435</v>
       </c>
       <c r="B9" t="s">
-        <v>310</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>318</v>
+        <v>436</v>
       </c>
       <c r="B10" t="s">
-        <v>319</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>320</v>
+        <v>438</v>
       </c>
       <c r="B11" t="s">
-        <v>321</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="B12" t="s">
-        <v>323</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>324</v>
+        <v>442</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>326</v>
+        <v>444</v>
       </c>
       <c r="B14" t="s">
-        <v>327</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>328</v>
+        <v>446</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>447</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>331</v>
+        <v>449</v>
       </c>
       <c r="B17" t="s">
-        <v>332</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>333</v>
+        <v>451</v>
       </c>
       <c r="B18" t="s">
-        <v>334</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>335</v>
+        <v>453</v>
       </c>
       <c r="B19" t="s">
-        <v>310</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>336</v>
+        <v>454</v>
       </c>
       <c r="B20" t="s">
-        <v>337</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="B21" t="s">
-        <v>339</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>340</v>
+        <v>458</v>
       </c>
       <c r="B22" t="s">
-        <v>337</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>462</v>
+      </c>
+      <c r="B24" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>463</v>
+      </c>
+      <c r="B25" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>465</v>
+      </c>
+      <c r="B26" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>467</v>
+      </c>
+      <c r="B27" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -4745,13 +6934,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>341</v>
+        <v>469</v>
       </c>
       <c r="B1" t="s">
-        <v>342</v>
+        <v>470</v>
       </c>
       <c r="C1" t="s">
-        <v>343</v>
+        <v>471</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -4759,13 +6948,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>472</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
-        <v>346</v>
+        <v>474</v>
       </c>
       <c r="D2" t="n">
         <v>31500000</v>
@@ -4773,13 +6962,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>347</v>
+        <v>475</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>476</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>477</v>
       </c>
       <c r="D3" t="n">
         <v>90000000</v>
@@ -4807,12 +6996,12 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>350</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>479</v>
       </c>
       <c r="B2" t="s">
         <v>144</v>
@@ -4821,12 +7010,12 @@
         <v>150000</v>
       </c>
       <c r="D2" t="s">
-        <v>352</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>481</v>
       </c>
       <c r="B3" t="s">
         <v>103</v>
@@ -4835,7 +7024,7 @@
         <v>45000</v>
       </c>
       <c r="D3" t="s">
-        <v>354</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/SD_rht_contracts.xlsx
+++ b/SD_rht_contracts.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t xml:space="preserve">state</t>
   </si>
@@ -146,6 +146,9 @@
     <t xml:space="preserve">first_seen_archive</t>
   </si>
   <si>
+    <t xml:space="preserve">basis_type</t>
+  </si>
+  <si>
     <t xml:space="preserve">SD</t>
   </si>
   <si>
@@ -1004,15 +1007,24 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00031</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00031, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+    <t xml:space="preserve">GENERAL KNOWLEDGE, LOW (owner's resolution of SD_SYSTEM_PARENTS_FORM_NOT_STATED, session 87): Sanford Health (Sioux Falls), the parent system of Sanford's South Dakota hospitals, which enrol with CMS under their own legal entities (e.g. SANFORD MEDICAL CENTER, SANFORD HEALTH NETWORK); 'SANFORD HEALTH' is not itself on CMS's SD Hospital Enrollments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§10.2 DIRECT: the recipient is a HEALTH-SYSTEM PARENT, typed HOSPITAL_OR_SYSTEM on general knowledge, not on the register (which states no form) and not on a CMS enrolment (none carries this string). No CCN; LOW, basis_type GENERAL_KNOWLEDGE, so the row is subtractable. Precedent: UVM Health Network and Southwestern Vermont Health (VT), Virtua (NJ). §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00031, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00031.html</t>
   </si>
   <si>
+    <t xml:space="preserve">SYSTEM_PARENT_GENERAL_KNOWLEDGE</t>
+  </si>
+  <si>
     <t xml:space="preserve">27RHT00031</t>
   </si>
   <si>
+    <t xml:space="preserve">GENERAL_KNOWLEDGE</t>
+  </si>
+  <si>
     <t xml:space="preserve">MOBRIDGE REGIONAL HOSPITAL</t>
   </si>
   <si>
@@ -1082,7 +1094,10 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00034</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00034, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+    <t xml:space="preserve">GENERAL KNOWLEDGE, LOW (owner's resolution of SD_SYSTEM_PARENTS_FORM_NOT_STATED, session 87): Avera Health (Sioux Falls), the parent system of Avera's South Dakota hospitals, which enrol with CMS under their own legal entities (e.g. AVERA MCKENNAN, AVERA ST LUKES); 'AVERA HEALTH' is not itself on CMS's SD Hospital Enrollments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§10.2 DIRECT: the recipient is a HEALTH-SYSTEM PARENT, typed HOSPITAL_OR_SYSTEM on general knowledge, not on the register (which states no form) and not on a CMS enrolment (none carries this string). No CCN; LOW, basis_type GENERAL_KNOWLEDGE, so the row is subtractable. Precedent: UVM Health Network and Southwestern Vermont Health (VT), Virtua (NJ). §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00034, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00034.html</t>
@@ -1409,19 +1424,19 @@
     <t xml:space="preserve">rows distributed_to_hospital = Yes</t>
   </si>
   <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dollars distributed_to_hospital = Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,643,252.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distinct hospitals among them</t>
+  </si>
+  <si>
     <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dollars distributed_to_hospital = Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,636,252.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distinct hospitals among them</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
   </si>
   <si>
     <t xml:space="preserve">round</t>
@@ -1928,52 +1943,55 @@
       <c r="AQ1" t="s">
         <v>42</v>
       </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
         <v>1462802</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P2"/>
       <c r="Q2"/>
@@ -1981,114 +1999,115 @@
       <c r="S2"/>
       <c r="T2"/>
       <c r="U2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V2"/>
       <c r="W2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AH2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI2" s="1" t="n">
         <v>46127</v>
       </c>
       <c r="AJ2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM2"/>
       <c r="AN2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AO2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP2"/>
       <c r="AQ2" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" t="n">
         <v>250000</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3"/>
       <c r="Q3"/>
@@ -2096,114 +2115,115 @@
       <c r="S3"/>
       <c r="T3"/>
       <c r="U3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V3"/>
       <c r="W3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA3" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>73</v>
-      </c>
       <c r="AB3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI3" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="AJ3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM3"/>
       <c r="AN3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP3"/>
       <c r="AQ3" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
         <v>399013</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P4"/>
       <c r="Q4"/>
@@ -2211,114 +2231,115 @@
       <c r="S4"/>
       <c r="T4"/>
       <c r="U4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V4"/>
       <c r="W4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA4" t="s">
         <v>85</v>
       </c>
-      <c r="Z4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>84</v>
-      </c>
       <c r="AB4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI4" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="AJ4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AM4"/>
       <c r="AN4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AO4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP4"/>
       <c r="AQ4" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="n">
         <v>225000</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5"/>
       <c r="Q5"/>
@@ -2326,114 +2347,115 @@
       <c r="S5"/>
       <c r="T5"/>
       <c r="U5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V5"/>
       <c r="W5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Z5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AA5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AH5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI5" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="AJ5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM5"/>
       <c r="AN5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP5"/>
       <c r="AQ5" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" t="n">
         <v>503000</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -2441,114 +2463,115 @@
       <c r="S6"/>
       <c r="T6"/>
       <c r="U6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V6"/>
       <c r="W6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y6" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA6" t="s">
         <v>107</v>
       </c>
-      <c r="Z6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>106</v>
-      </c>
       <c r="AB6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI6" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="AJ6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AK6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AM6"/>
       <c r="AN6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AO6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP6"/>
       <c r="AQ6" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D7" t="n">
         <v>567350</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -2556,114 +2579,115 @@
       <c r="S7"/>
       <c r="T7"/>
       <c r="U7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V7"/>
       <c r="W7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y7" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA7" t="s">
         <v>117</v>
       </c>
-      <c r="Z7" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>116</v>
-      </c>
       <c r="AB7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AH7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI7" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="AJ7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AK7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AL7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AM7"/>
       <c r="AN7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AO7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP7"/>
       <c r="AQ7" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D8" t="n">
         <v>450000</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -2671,114 +2695,115 @@
       <c r="S8"/>
       <c r="T8"/>
       <c r="U8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V8"/>
       <c r="W8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y8" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA8" t="s">
         <v>128</v>
       </c>
-      <c r="Z8" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>127</v>
-      </c>
       <c r="AB8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI8" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="AJ8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AK8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AL8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM8"/>
       <c r="AN8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP8"/>
       <c r="AQ8" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D9" t="n">
         <v>226930</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -2786,112 +2811,113 @@
       <c r="S9"/>
       <c r="T9"/>
       <c r="U9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V9"/>
       <c r="W9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y9" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA9" t="s">
         <v>139</v>
       </c>
-      <c r="Z9" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>138</v>
-      </c>
       <c r="AB9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF9"/>
       <c r="AG9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI9" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL9"/>
       <c r="AM9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AO9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP9"/>
       <c r="AQ9" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
         <v>130571</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -2899,112 +2925,113 @@
       <c r="S10"/>
       <c r="T10"/>
       <c r="U10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V10"/>
       <c r="W10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y10" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA10" t="s">
         <v>147</v>
       </c>
-      <c r="Z10" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>146</v>
-      </c>
       <c r="AB10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF10"/>
       <c r="AG10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AH10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI10" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL10"/>
       <c r="AM10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AO10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP10"/>
       <c r="AQ10" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
         <v>170816</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -3012,112 +3039,113 @@
       <c r="S11"/>
       <c r="T11"/>
       <c r="U11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V11"/>
       <c r="W11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y11" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA11" t="s">
         <v>153</v>
       </c>
-      <c r="Z11" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>152</v>
-      </c>
       <c r="AB11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF11"/>
       <c r="AG11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL11"/>
       <c r="AM11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP11"/>
       <c r="AQ11" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>88800</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -3125,114 +3153,115 @@
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V12"/>
       <c r="W12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y12" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA12" t="s">
         <v>161</v>
       </c>
-      <c r="Z12" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>160</v>
-      </c>
       <c r="AB12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AH12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI12" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AM12"/>
       <c r="AN12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AO12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP12"/>
       <c r="AQ12" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D13" t="n">
         <v>425000</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -3240,114 +3269,115 @@
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V13"/>
       <c r="W13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y13" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA13" t="s">
         <v>170</v>
       </c>
-      <c r="Z13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>169</v>
-      </c>
       <c r="AB13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AH13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI13" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="AJ13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AK13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM13"/>
       <c r="AN13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP13"/>
       <c r="AQ13" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" t="n">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D14" t="n">
         <v>719085</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -3355,114 +3385,115 @@
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V14"/>
       <c r="W14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y14" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA14" t="s">
         <v>180</v>
       </c>
-      <c r="Z14" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>179</v>
-      </c>
       <c r="AB14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AH14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI14" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="AJ14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM14"/>
       <c r="AN14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AO14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP14"/>
       <c r="AQ14" t="s">
-        <v>69</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AR14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D15" t="n">
         <v>133352</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P15"/>
       <c r="Q15"/>
@@ -3470,114 +3501,115 @@
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15" t="s">
+        <v>189</v>
+      </c>
+      <c r="V15" t="s">
+        <v>190</v>
+      </c>
+      <c r="W15" t="s">
+        <v>57</v>
+      </c>
+      <c r="X15" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA15" t="s">
         <v>188</v>
       </c>
-      <c r="V15" t="s">
-        <v>189</v>
-      </c>
-      <c r="W15" t="s">
-        <v>56</v>
-      </c>
-      <c r="X15" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>187</v>
-      </c>
       <c r="AB15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF15"/>
       <c r="AG15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI15" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL15"/>
       <c r="AM15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AO15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP15"/>
       <c r="AQ15" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D16" t="n">
         <v>467790</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P16"/>
       <c r="Q16"/>
@@ -3585,114 +3617,115 @@
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V16"/>
       <c r="W16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y16" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA16" t="s">
         <v>201</v>
       </c>
-      <c r="Z16" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>200</v>
-      </c>
       <c r="AB16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF16"/>
       <c r="AG16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AH16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI16" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL16"/>
       <c r="AM16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ16" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D17" t="n">
         <v>324000</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
@@ -3700,116 +3733,117 @@
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V17"/>
       <c r="W17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y17" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA17" t="s">
         <v>211</v>
       </c>
-      <c r="Z17" t="s">
-        <v>212</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>210</v>
-      </c>
       <c r="AB17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AH17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI17" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AK17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM17"/>
       <c r="AN17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ17" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="n">
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D18" t="n">
         <v>370562</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
@@ -3817,116 +3851,117 @@
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y18" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA18" t="s">
         <v>219</v>
       </c>
-      <c r="Z18" t="s">
-        <v>220</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>218</v>
-      </c>
       <c r="AB18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF18"/>
       <c r="AG18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AH18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI18" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AK18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL18"/>
       <c r="AM18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ18" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" t="n">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D19" t="n">
         <v>145500</v>
       </c>
       <c r="E19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P19"/>
       <c r="Q19"/>
@@ -3934,114 +3969,115 @@
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V19"/>
       <c r="W19" t="s">
+        <v>229</v>
+      </c>
+      <c r="X19" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA19" t="s">
         <v>228</v>
       </c>
-      <c r="X19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>229</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>227</v>
-      </c>
       <c r="AB19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF19"/>
       <c r="AG19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI19" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL19"/>
       <c r="AM19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ19" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" t="n">
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" t="n">
         <v>307228</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
@@ -4049,114 +4085,115 @@
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V20"/>
       <c r="W20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y20" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA20" t="s">
         <v>235</v>
       </c>
-      <c r="Z20" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>234</v>
-      </c>
       <c r="AB20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AH20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI20" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AK20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM20"/>
       <c r="AN20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP20"/>
       <c r="AQ20" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>449402</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -4164,114 +4201,115 @@
       <c r="S21"/>
       <c r="T21"/>
       <c r="U21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V21"/>
       <c r="W21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y21" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA21" t="s">
         <v>242</v>
       </c>
-      <c r="Z21" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>241</v>
-      </c>
       <c r="AB21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AH21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI21" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AK21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM21"/>
       <c r="AN21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP21"/>
       <c r="AQ21" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" t="n">
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D22" t="n">
         <v>185676</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P22"/>
       <c r="Q22"/>
@@ -4279,471 +4317,475 @@
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V22"/>
       <c r="W22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y22" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA22" t="s">
         <v>249</v>
       </c>
-      <c r="Z22" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>248</v>
-      </c>
       <c r="AB22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG22" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AH22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI22" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM22"/>
       <c r="AN22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP22"/>
       <c r="AQ22" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" t="n">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D23" t="n">
         <v>38000</v>
       </c>
       <c r="E23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23"/>
       <c r="T23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="U23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V23"/>
       <c r="W23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AB23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF23"/>
       <c r="AG23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AH23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI23" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AK23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL23"/>
       <c r="AM23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ23" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" t="n">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D24" t="n">
         <v>181600</v>
       </c>
       <c r="E24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q24"/>
       <c r="R24"/>
       <c r="S24"/>
       <c r="T24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="U24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V24"/>
       <c r="W24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AB24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AF24"/>
       <c r="AG24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AH24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI24" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AK24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL24"/>
       <c r="AM24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ24" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D25" t="n">
         <v>103700</v>
       </c>
       <c r="E25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q25"/>
       <c r="R25"/>
       <c r="S25"/>
       <c r="T25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V25"/>
       <c r="W25" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Z25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AB25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF25"/>
       <c r="AG25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AH25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI25" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AK25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL25"/>
       <c r="AM25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ25" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" t="n">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D26" t="n">
         <v>248000</v>
       </c>
       <c r="E26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K26" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P26"/>
       <c r="Q26"/>
@@ -4751,114 +4793,115 @@
       <c r="S26"/>
       <c r="T26"/>
       <c r="U26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V26"/>
       <c r="W26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y26" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA26" t="s">
         <v>286</v>
       </c>
-      <c r="Z26" t="s">
-        <v>287</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>285</v>
-      </c>
       <c r="AB26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF26"/>
       <c r="AG26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AH26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI26" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AK26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL26"/>
       <c r="AM26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ26" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D27" t="n">
         <v>650000</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P27"/>
       <c r="Q27"/>
@@ -4866,114 +4909,115 @@
       <c r="S27"/>
       <c r="T27"/>
       <c r="U27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V27"/>
       <c r="W27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y27" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>296</v>
+      </c>
+      <c r="AA27" t="s">
         <v>294</v>
       </c>
-      <c r="Z27" t="s">
-        <v>295</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>293</v>
-      </c>
       <c r="AB27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AH27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI27" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="AJ27" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK27" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM27"/>
       <c r="AN27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP27"/>
       <c r="AQ27" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AR27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28" t="n">
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D28" t="n">
         <v>1258349</v>
       </c>
       <c r="E28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P28"/>
       <c r="Q28"/>
@@ -4981,114 +5025,115 @@
       <c r="S28"/>
       <c r="T28"/>
       <c r="U28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V28"/>
       <c r="W28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y28" t="s">
+        <v>306</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>307</v>
+      </c>
+      <c r="AA28" t="s">
         <v>305</v>
       </c>
-      <c r="Z28" t="s">
-        <v>306</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>304</v>
-      </c>
       <c r="AB28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF28"/>
       <c r="AG28" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AH28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI28" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ28" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL28"/>
       <c r="AM28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO28" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ28" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" t="n">
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D29" t="n">
         <v>349047</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K29" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
@@ -5096,943 +5141,955 @@
       <c r="S29"/>
       <c r="T29"/>
       <c r="U29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y29" t="s">
+        <v>314</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA29" t="s">
         <v>313</v>
       </c>
-      <c r="Z29" t="s">
-        <v>314</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>312</v>
-      </c>
       <c r="AB29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF29"/>
       <c r="AG29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AH29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI29" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL29"/>
       <c r="AM29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AP29"/>
       <c r="AQ29" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" t="n">
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D30" t="n">
         <v>418563</v>
       </c>
       <c r="E30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P30" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="U30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V30"/>
       <c r="W30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AB30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF30"/>
       <c r="AG30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AH30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI30" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL30"/>
       <c r="AM30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN30" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ30" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B31" t="n">
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D31" t="n">
         <v>5442000</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31"/>
       <c r="S31"/>
-      <c r="T31"/>
+      <c r="T31" t="s">
+        <v>330</v>
+      </c>
       <c r="U31" t="s">
-        <v>188</v>
-      </c>
-      <c r="V31" t="s">
         <v>189</v>
       </c>
+      <c r="V31"/>
       <c r="W31" t="s">
-        <v>56</v>
+        <v>229</v>
       </c>
       <c r="X31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Y31" t="s">
+        <v>331</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA31" t="s">
         <v>329</v>
       </c>
-      <c r="Z31" t="s">
-        <v>330</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>328</v>
-      </c>
       <c r="AB31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE31" t="s">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="AF31"/>
       <c r="AG31" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AH31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI31" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL31"/>
       <c r="AM31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP31" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ31" t="s">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" t="n">
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D32" t="n">
         <v>2704989</v>
       </c>
       <c r="E32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G32" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K32" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L32" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P32" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32"/>
       <c r="T32" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="U32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V32"/>
       <c r="W32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y32" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Z32" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA32" t="s">
         <v>339</v>
       </c>
-      <c r="AA32" t="s">
-        <v>335</v>
-      </c>
       <c r="AB32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF32"/>
       <c r="AG32" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AH32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI32" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ32" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AK32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL32"/>
       <c r="AM32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ32" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" t="n">
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D33" t="n">
         <v>2699907</v>
       </c>
       <c r="E33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K33" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="L33" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="M33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P33" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q33"/>
       <c r="R33"/>
       <c r="S33"/>
       <c r="T33" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="U33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V33"/>
       <c r="W33" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y33" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Z33" t="s">
+        <v>353</v>
+      </c>
+      <c r="AA33" t="s">
         <v>349</v>
       </c>
-      <c r="AA33" t="s">
-        <v>345</v>
-      </c>
       <c r="AB33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE33" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AF33"/>
       <c r="AG33" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AH33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI33" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ33" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AK33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL33"/>
       <c r="AM33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN33" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO33" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ33" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" t="n">
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D34" t="n">
         <v>1565000</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K34" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L34" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34"/>
       <c r="S34"/>
-      <c r="T34"/>
+      <c r="T34" t="s">
+        <v>359</v>
+      </c>
       <c r="U34" t="s">
-        <v>188</v>
-      </c>
-      <c r="V34" t="s">
         <v>189</v>
       </c>
+      <c r="V34"/>
       <c r="W34" t="s">
-        <v>56</v>
+        <v>229</v>
       </c>
       <c r="X34" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Y34" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Z34" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AA34" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AB34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE34" t="s">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="AF34"/>
       <c r="AG34" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AH34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI34" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL34"/>
       <c r="AM34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN34" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ34" t="s">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" t="n">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D35" t="n">
         <v>77432</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K35" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="L35" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q35"/>
       <c r="R35"/>
       <c r="S35"/>
       <c r="T35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="U35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V35"/>
       <c r="W35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y35" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Z35" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AA35" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AB35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF35"/>
       <c r="AG35" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AH35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI35" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AK35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL35"/>
       <c r="AM35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN35" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AO35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ35" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" t="n">
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D36" t="n">
         <v>175000</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G36" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K36" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="L36" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="M36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P36" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q36"/>
       <c r="R36"/>
       <c r="S36"/>
       <c r="T36" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="U36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V36"/>
       <c r="W36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y36" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Z36" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AA36" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AB36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF36"/>
       <c r="AG36" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AH36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI36" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ36" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AK36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL36"/>
       <c r="AM36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN36" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AO36" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP36" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ36" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D37" t="n">
         <v>80431</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="L37" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P37"/>
       <c r="Q37"/>
@@ -6040,235 +6097,237 @@
       <c r="S37"/>
       <c r="T37"/>
       <c r="U37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y37" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z37" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AA37" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AB37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF37"/>
       <c r="AG37" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AH37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI37" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ37" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL37"/>
       <c r="AM37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN37" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AO37" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP37" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ37" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" t="n">
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D38" t="n">
         <v>1585212</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G38" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K38" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="L38" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="M38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P38" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q38"/>
       <c r="R38"/>
       <c r="S38"/>
       <c r="T38" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="U38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V38"/>
       <c r="W38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y38" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Z38" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AA38" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AB38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AF38"/>
       <c r="AG38" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AH38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI38" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="AJ38" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AK38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL38"/>
       <c r="AM38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN38" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AO38" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP38" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ38" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" t="n">
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D39" t="n">
         <v>999242</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="H39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K39" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="L39" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P39"/>
       <c r="Q39"/>
@@ -6276,116 +6335,117 @@
       <c r="S39"/>
       <c r="T39"/>
       <c r="U39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V39"/>
       <c r="W39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y39" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Z39" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AA39" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AB39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG39" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AH39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI39" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="AJ39" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AK39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM39"/>
       <c r="AN39" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AO39" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP39" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ39" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B40" t="n">
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D40" t="n">
         <v>175000</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K40" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="L40" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P40"/>
       <c r="Q40"/>
@@ -6393,116 +6453,117 @@
       <c r="S40"/>
       <c r="T40"/>
       <c r="U40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y40" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="Z40" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AA40" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AB40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF40"/>
       <c r="AG40" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="AH40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI40" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="AJ40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL40"/>
       <c r="AM40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN40" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AO40" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP40" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ40" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n">
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D41" t="n">
         <v>62795</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K41" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="L41" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P41"/>
       <c r="Q41"/>
@@ -6510,116 +6571,117 @@
       <c r="S41"/>
       <c r="T41"/>
       <c r="U41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y41" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Z41" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AA41" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AB41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF41"/>
       <c r="AG41" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AH41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI41" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="AJ41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AK41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL41"/>
       <c r="AM41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AN41" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP41" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ41" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n">
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D42" t="n">
         <v>20000</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G42" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K42" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="L42" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="M42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P42"/>
       <c r="Q42"/>
@@ -6627,72 +6689,73 @@
       <c r="S42"/>
       <c r="T42"/>
       <c r="U42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y42" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="Z42" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AA42" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AB42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG42" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AH42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI42" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="AJ42" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AK42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AL42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM42"/>
       <c r="AN42" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AO42" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AP42" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AQ42" t="s">
-        <v>309</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AR42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6707,218 +6770,218 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B4" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B7" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B8" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B9" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B10" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B12" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B13" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B14" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B15" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B16" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B17" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B18" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B19" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B20" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B21" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B22" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B23" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B24" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B25" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B26" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B27" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -6934,13 +6997,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -6948,13 +7011,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D2" t="n">
         <v>31500000</v>
@@ -6962,13 +7025,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D3" t="n">
         <v>90000000</v>
@@ -6996,35 +7059,35 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C2" t="n">
         <v>150000</v>
       </c>
       <c r="D2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
         <v>45000</v>
       </c>
       <c r="D3" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/SD_rht_contracts.xlsx
+++ b/SD_rht_contracts.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
   <si>
     <t xml:space="preserve">state</t>
   </si>
@@ -305,495 +305,495 @@
     <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=26RHT00006</t>
   </si>
   <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00006, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/26RHT00006.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract with State or Local Government Agency (5-18D-21(8))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26RHT00006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROOKINGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose of the contract is to implement Chronic Disease Self-Management Programming.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLACK HILLS SPECIAL SERVICES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09rht-003 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | STURGIS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: South Dakota education service cooperative, a nonprofit. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00001, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00001.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09rht-003 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STURGIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To provide project management support for the Chronic Disease Management Initiative for Rural Health Transformation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUIDEHOUSE INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09RHT-013 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | CHICAGO, IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: national management consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00005, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00005.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09RHT-013 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHICAGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduct the Statewide Maternal Health Access and Services Assessment for the Rural Health Transformation Project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYERS &amp; STAUFFER LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-08RHT-008 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | KANSAS CITY, MO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: actuarial and accounting firm engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00007, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00007.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 26-08RHT-008 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KANSAS CITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose of this contract is to assist the State in developing a population-based alternative payment methodology for South Dakota Medicaid primary care services that incentivizes providers and patients and promotes shared accountability for cost and utilization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE GENERATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | SIOUX FALLS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: Sioux Falls nonprofit senior services centre. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00008, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00008.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Develop, launch, and evaluate a Caregiver Concierge mobile application that includes guidance, access to educational resources, register for support groups and classes, and receive referrals to available services in South Dakota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD FOUNDATION FOR MEDICAL CARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00009, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00009.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruit and support individuals from priority and underserved communities to participate in doula training and certification. Provide mentorship, assist, and facilitate partnerships between community-based doulas and healthcare providers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00010, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00010.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Health Transformation initiative is a statewide effort focused on strengthening rural healthcare systems and improving access to quality care across South Dakota. Through strategic investments, innovative care models, and cross-agency collaboration, Rural Health Transformation is designed to build a more resilient, connected, and sustainable rural health system for communities across the state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTHEAST TECHNICAL COLLEGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | Sole Source Services (5-18D-21(1)) | SIOUX FALLS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00011, begun 2026-08-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00011.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sole Source Services (5-18D-21(1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offer specialized training and certificaiton/education for CHWs and CHRs in South Dakota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEALTH MANAGEMENT ASSOCIATES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-08RHT-015 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | OKEMOS, MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: commercial health policy consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00012, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00012.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 26-08RHT-015 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKEMOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This vendor will assist in evaluating the current billing, data collection, and reporting systems of DBH, South Dakota Medicaid, and identified providers working toward CCBHC certification or becoming a Designated Collaborating Organization (DCO) and provide a technology roadmap that supports South Dakota and provider systems to function with CCBHC data collection, reporting, and billing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09RHT-018 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | SIOUX FALLS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00013, begun 2026-07-17. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00013.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09RHT-018 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To establish regional EMS hubs that improve coordination, resource sharing, operational efficiency, and overall system performance across South Dakota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTH DAKOTA DOULAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPIENT_TYPE_INFERRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00014, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00014.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALLBACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expand and strengthen the doula workforce in South Dakota through recruitment, training, certification, and workforce development activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24_open_sd_contract_search_RHT.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD URBAN INDIAN HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBAL_ORG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | PIERRE, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a tribal entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00015, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00015.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHT series - Rural Strong grants (subset of the 28-grant, $31.5M round of 2026-07-23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSITY OF SOUTH DAKOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | Contract with State or Local Government Agency (5-18D-21(8)) | VERMILLION, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00016, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00016.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERMILLION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETE HEALTH CENTER OF BH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | RAPID CITY, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00017, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00017.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPID CITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMUNITY MEMORIAL HOSPITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOSPITAL_OR_SYSTEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | BURKE, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00018, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00018.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00019, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00019.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design, implement, host, and maintain a statewide education and training platform that expands access to high-quality, accredited training for all healthcare professionals in South Dakota, with a particular emphasis on supporting rural healthcare providers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09RHT-022 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | STURGIS, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: South Dakota education service cooperative, a nonprofit. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00020, begun 2026-08-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00020.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09RHT-022 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide strategic leadership and operational support within the Office of Rural Health and Emergency Services in advancing rural healthcare transformation initiatives across the state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00021, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00021.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAULKTON AREA MEDICAL CENTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | FAULKTON, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city FAULKTON, CCN 431301, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/MEDIUM.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 26RHT00006, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/26RHT00006.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contract with State or Local Government Agency (5-18D-21(8))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26RHT00006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROOKINGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The purpose of the contract is to implement Chronic Disease Self-Management Programming.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLACK HILLS SPECIAL SERVICES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09rht-003 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | STURGIS, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: South Dakota education service cooperative, a nonprofit. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00001, begun 2026-05-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00001.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09rht-003 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STURGIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To provide project management support for the Chronic Disease Management Initiative for Rural Health Transformation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUIDEHOUSE INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09RHT-013 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | CHICAGO, IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: national management consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00005, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00005.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09RHT-013 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHICAGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conduct the Statewide Maternal Health Access and Services Assessment for the Rural Health Transformation Project.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYERS &amp; STAUFFER LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-08RHT-008 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | KANSAS CITY, MO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: actuarial and accounting firm engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00007, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00007.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFP (Linked) RFP Number: 26-08RHT-008 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KANSAS CITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The purpose of this contract is to assist the State in developing a population-based alternative payment methodology for South Dakota Medicaid primary care services that incentivizes providers and patients and promotes shared accountability for cost and utilization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVE GENERATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | NA | SIOUX FALLS, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: Sioux Falls nonprofit senior services centre. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00008, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00008.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Develop, launch, and evaluate a Caregiver Concierge mobile application that includes guidance, access to educational resources, register for support groups and classes, and receive referrals to available services in South Dakota.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD FOUNDATION FOR MEDICAL CARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00009, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00009.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recruit and support individuals from priority and underserved communities to participate in doula training and certification. Provide mentorship, assist, and facilitate partnerships between community-based doulas and healthcare providers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00010, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00010.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Health Transformation initiative is a statewide effort focused on strengthening rural healthcare systems and improving access to quality care across South Dakota. Through strategic investments, innovative care models, and cross-agency collaboration, Rural Health Transformation is designed to build a more resilient, connected, and sustainable rural health system for communities across the state.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTHEAST TECHNICAL COLLEGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | Sole Source Services (5-18D-21(1)) | SIOUX FALLS, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00011, begun 2026-08-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00011.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sole Source Services (5-18D-21(1))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offer specialized training and certificaiton/education for CHWs and CHRs in South Dakota.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEALTH MANAGEMENT ASSOCIATES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-08RHT-015 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | OKEMOS, MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: commercial health policy consultancy engaged through an RFP for services. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00012, begun 2026-06-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00012.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFP (Linked) RFP Number: 26-08RHT-015 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OKEMOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This vendor will assist in evaluating the current billing, data collection, and reporting systems of DBH, South Dakota Medicaid, and identified providers working toward CCBHC certification or becoming a Designated Collaborating Organization (DCO) and provide a technology roadmap that supports South Dakota and provider systems to function with CCBHC data collection, reporting, and billing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09RHT-018 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | SIOUX FALLS, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: South Dakota Foundation for Medical Care, the state's nonprofit quality improvement organisation. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00013, begun 2026-07-17. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00013.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09RHT-018 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To establish regional EMS hubs that improve coordination, resource sharing, operational efficiency, and overall system performance across South Dakota.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTH DAKOTA DOULAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECIPIENT_TYPE_INFERRED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00014, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00014.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALLBACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expand and strengthen the doula workforce in South Dakota through recruitment, training, certification, and workforce development activities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24_open_sd_contract_search_RHT.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD URBAN INDIAN HEALTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIBAL_ORG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | NA | PIERRE, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient name rule: name states a tribal entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00015, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00015.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHT series - Rural Strong grants (subset of the 28-grant, $31.5M round of 2026-07-23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSITY OF SOUTH DAKOTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | Contract with State or Local Government Agency (5-18D-21(8)) | VERMILLION, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00016, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00016.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERMILLION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPLETE HEALTH CENTER OF BH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | NA | RAPID CITY, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00017, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00017.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAPID CITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMMUNITY MEMORIAL HOSPITAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOSPITAL_OR_SYSTEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | NA | BURKE, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIRECT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00018, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00018.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BURKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00019, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00019.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design, implement, host, and maintain a statewide education and training platform that expands access to high-quality, accredited training for all healthcare professionals in South Dakota, with a particular emphasis on supporting rural healthcare providers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | RFP (Linked) RFP Number: 26-09RHT-022 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/ | STURGIS, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: South Dakota education service cooperative, a nonprofit. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00020, begun 2026-08-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00020.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFP (Linked) RFP Number: 26-09RHT-022 Solicitation Link: https://boa.sd.gov/central-services/procurement-management/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provide strategic leadership and operational support within the Office of Rural Health and Emergency Services in advancing rural healthcare transformation initiatives across the state.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00021, begun 2026-07-01. This is ADMINISTRATIVE RHTP spend and is NOT part of South Dakota's announced $31.5M (28 projects) or $90M (82 organisations) rounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00021.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27RHT00021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAULKTON AREA MEDICAL CENTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 - HEALTH | NA | FAULKTON, SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city FAULKTON, CCN 431301, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Recipient name rule: name states a medical center. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00022, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
   </si>
   <si>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">431316</t>
   </si>
   <si>
-    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): DOING BUSINESS AS NAME = the register's own string, city REDFIELD, CCN 431316, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): DOING BUSINESS AS NAME = the register's own string, city REDFIELD, CCN 431316, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/MEDIUM.</t>
   </si>
   <si>
     <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00024, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">431318</t>
   </si>
   <si>
-    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city BOWDLE, CCN 431318, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city BOWDLE, CCN 431318, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/MEDIUM.</t>
   </si>
   <si>
     <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00030, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">431325</t>
   </si>
   <si>
-    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city MOBRIDGE, CCN 431325, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/HIGH.</t>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): ORGANIZATION NAME = the register's own string, city MOBRIDGE, CCN 431325, PART A PROVIDER - CRITICAL ACCESS HOSPITAL. Machine answer on the name: HOSPITAL_OR_SYSTEM/MEDIUM.</t>
   </si>
   <si>
     <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00032, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
@@ -1289,6 +1289,300 @@
     <t xml:space="preserve">The purpose is to provide contractual Technical Assistance and Support to assist with their EHR planning.</t>
   </si>
   <si>
+    <t xml:space="preserve">KRISTIN R TEIGEN PL, ABDN DENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | ABERDEEN, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00027, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00027.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABERDEEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12_open_sd_contract_search_RHT.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UROLOGY SPECIALISTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00042, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Urology Specialists: 'fund EHR enhancements, SD HIE connection, clinical technology, and training'. Reads like the $90M round's EHR modernisation; the register does not name the round.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00042.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is to fund EHR enhancements, SD HIE connection, clinical technology, and training.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRAIRIE LAKES HEALTH CARE SYST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | WATERTOWN, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">430005A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): PRAIRIE LAKES HEALTH CARE SYSTEM INC, WATERTOWN, CCN 430005A, PART A PROVIDER - HOSPITAL. HAND-READ BRIDGE (LEGAL_NAME_TRUNCATED, session 99): the register truncates vendor names at 30 characters and prints 'PRAIRIE LAKES HEALTH CARE SYST'. Machine answer on the name: NONPROFIT_CBO/LOW.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§10.2 DIRECT on a HAND-READ CMS ENROLMENT BRIDGE (LEGAL_NAME_TRUNCATED): CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): PRAIRIE LAKES HEALTH CARE SYSTEM INC, WATERTOWN, CCN 430005A, PART A PROVIDER - HOSPITAL. The register states no form and its string is not the enrolled name exactly, so the bridge is a human judgement and the row is LOW (the OK RRR precedent, session 86; basis_type GENERAL_KNOWLEDGE keeps it subtractable). HIGH waits on Stage 5's CCN match. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00043, begun 2026-07-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Prairie Lakes Health Care System: 'implement chronic disease management activities' -- the wording of Faulkton's, Mobridge's and Avera at Home's unplaced contracts. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00043.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS_ENROLMENT_BRIDGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WATERTOWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAKESIDE PAIN CENTER PROF LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00044, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Lakeside Pain Center: 'fund EHR enhancements and cyber security infrastructure'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00044.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is to fund EHR enhancements and cyber security infrastructure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THREE RIVERS MENTAL HEALTH &amp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | LEMMON, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00046, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Three Rivers Mental Health: 'fund the EHR replacement'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00046.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEMMON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is to fund the EHR replacement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONUMENT HEALTH RAPID CITY HOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">430077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): MONUMENT HEALTH RAPID CITY HOSPITAL INC (dba MONUMENT HEALTH RAPID CITY HOSPITAL), RAPID CITY, CCN 430077, PART A PROVIDER - HOSPITAL. HAND-READ BRIDGE (LEGAL_NAME_TRUNCATED, session 99): the register truncates vendor names at 30 characters and prints 'MONUMENT HEALTH RAPID CITY HOS'. Machine answer on the name: NONPROFIT_CBO/LOW.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§10.2 DIRECT on a HAND-READ CMS ENROLMENT BRIDGE (LEGAL_NAME_TRUNCATED): CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): MONUMENT HEALTH RAPID CITY HOSPITAL INC (dba MONUMENT HEALTH RAPID CITY HOSPITAL), RAPID CITY, CCN 430077, PART A PROVIDER - HOSPITAL. The register states no form and its string is not the enrolled name exactly, so the bridge is a human judgement and the row is LOW (the OK RRR precedent, session 86; basis_type GENERAL_KNOWLEDGE keeps it subtractable). HIGH waits on Stage 5's CCN match. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00048, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00048.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUSHMORE AMBULATORY SURGERY CE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00049, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00049.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORTHERN HILLS TRAINING CENTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | SPEARFISH, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00050, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Northern Hills Training Center: 'purchase equipment'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00050.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPEARFISH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is purchase equipment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVERA HEART HOSPITAL OF SD LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">430095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): HEART HOSPITAL OF SOUTH DAKOTA LLC (dba AVERA HEART HOSPITAL OF SOUTH DAKOTA), SIOUX FALLS, CCN 430095, PART A PROVIDER - HOSPITAL. HAND-READ BRIDGE (DBA_OF_LEGAL_ENTITY, session 99): the register truncates vendor names at 30 characters and prints 'AVERA HEART HOSPITAL OF SD LLC'. Machine answer on the name: HOSPITAL_OR_SYSTEM/MEDIUM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§10.2 DIRECT on a HAND-READ CMS ENROLMENT BRIDGE (DBA_OF_LEGAL_ENTITY): CMS Hospital Enrollments (archived data/evidence/SD/federal_records/2026-09-24/cms_hosp_enrollments_SD.json): HEART HOSPITAL OF SOUTH DAKOTA LLC (dba AVERA HEART HOSPITAL OF SOUTH DAKOTA), SIOUX FALLS, CCN 430095, PART A PROVIDER - HOSPITAL. The register states no form and its string is not the enrolled name exactly, so the bridge is a human judgement and the row is LOW (the OK RRR precedent, session 86; basis_type GENERAL_KNOWLEDGE keeps it subtractable). HIGH waits on Stage 5's CCN match. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00051, begun 2026-08-01. This is a RURAL STRONG GRANT -- the register's own description is 'Implementation of a Rural Strong Grant as a part of the federal Rural Health Transformation Program' -- one of the 28 grants ($31.5M) South Dakota announced on 2026-07-23 (KB0046839). It is INSIDE that round total and NEVER in addition to it: sd_year1_awardees.csv carries the round as one aggregate row whose round_amount ($31,500,000) already includes this contract. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00051.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a tribal entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00052, begun 2026-07-01. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: SD Urban Indian Health: 'implement chronic disease management activities'. No round named; its 2026-09 contract 27RHT00015 is a separate award.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00052.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGHLAND HILLS LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 - HEALTH | NA | BELLE FOURCHE, SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00053, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Highland Hills LLC: 'fund a western South Dakota Regional Innovation Center'. KB0047023 names Regional Innovation Centers (DSU's 27RHT00039 is the same shape); the register does not name the round.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00053.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELLE FOURCHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The purpose is to fund a western South Dakota Regional Innovation Center to advance technology-enabled solutions that improve aging, chronic disease management, caregiver support, and healthcare workforce capacity."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTER FOR FAMILY MEDICINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHYSICIAN_PRACTICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota Open SD - Grants and Contracts register, contract 27RHT00054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.sd.gov/contractsDocShow.aspx?DocID=27RHT00054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: name states a clinical practice. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: South Dakota's Grants and Contracts register (SDCL 1-56-10 / 1-27-46), contract 27RHT00054, begun 2026-02-20. This is a NAMED RHTP AWARD WHOSE ROUND THE REGISTER DOES NOT STATE (placed by hand, session 86: Center for Family Medicine: 'purchase equipment and train employees on technology'. No round named.). It MAY sit inside the $90M Technology and data round of 2026-08-19 (KB0047023) or outside both announced rounds; in neither case is it ever added to a round total. Tier 3, named recipient, primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/evidence/SD/contract_details/27RHT00054.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27RHT00054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose is to purchase equipment and train employees on technology.</t>
+  </si>
+  <si>
     <t xml:space="preserve">measure</t>
   </si>
   <si>
@@ -1298,19 +1592,19 @@
     <t xml:space="preserve">contracts extracted from the RHT series</t>
   </si>
   <si>
-    <t xml:space="preserve">41</t>
+    <t xml:space="preserve">53</t>
   </si>
   <si>
     <t xml:space="preserve">distinct vendor strings</t>
   </si>
   <si>
-    <t xml:space="preserve">33</t>
+    <t xml:space="preserve">44</t>
   </si>
   <si>
     <t xml:space="preserve">total extracted (ALL THREE pools; never add to sd_year1_awardees.csv round totals)</t>
   </si>
   <si>
-    <t xml:space="preserve">26,836,144.00</t>
+    <t xml:space="preserve">37,039,799.00</t>
   </si>
   <si>
     <t xml:space="preserve">-- POOL 1: ADMINISTRATIVE --</t>
@@ -1343,13 +1637,13 @@
     <t xml:space="preserve">Rural Strong grant contracts on the register</t>
   </si>
   <si>
-    <t xml:space="preserve">14 of the 28 announced 2026-07-23</t>
+    <t xml:space="preserve">18 of the 28 announced 2026-07-23</t>
   </si>
   <si>
     <t xml:space="preserve">Rural Strong total on the register</t>
   </si>
   <si>
-    <t xml:space="preserve">15,967,960.00</t>
+    <t xml:space="preserve">25,012,010.00</t>
   </si>
   <si>
     <t xml:space="preserve">Rural Strong round total (KB0046839)</t>
@@ -1367,7 +1661,7 @@
     <t xml:space="preserve">Rural Strong grants not yet on the register</t>
   </si>
   <si>
-    <t xml:space="preserve">14 -- NAMED NOWHERE; their amount is stated by no source and is NOT computed here (§6.2)</t>
+    <t xml:space="preserve">10 -- NAMED NOWHERE; their amount is stated by no source and is NOT computed here (§6.2)</t>
   </si>
   <si>
     <t xml:space="preserve">-- POOL 3: NAMED AWARDS, ROUND NOT STATED (Tier 3) --</t>
@@ -1376,13 +1670,13 @@
     <t xml:space="preserve">unplaced award contracts on the register</t>
   </si>
   <si>
-    <t xml:space="preserve">8</t>
+    <t xml:space="preserve">16</t>
   </si>
   <si>
     <t xml:space="preserve">unplaced total</t>
   </si>
   <si>
-    <t xml:space="preserve">3,175,112.00</t>
+    <t xml:space="preserve">4,334,717.00</t>
   </si>
   <si>
     <t xml:space="preserve">relationship to the rounds</t>
@@ -1397,13 +1691,13 @@
     <t xml:space="preserve">Technology/data round announced 2026-08-19</t>
   </si>
   <si>
-    <t xml:space="preserve">$90,000,000 to 82 rural healthcare organizations -- NO contract on open.sd.gov names this round; 8 unplaced contracts ($3,175,112.00) may be among them</t>
+    <t xml:space="preserve">$90,000,000 to 82 rural healthcare organizations -- NO contract on open.sd.gov names this round; 16 unplaced contracts ($4,334,717.00) may be among them</t>
   </si>
   <si>
     <t xml:space="preserve">Rural Strong + unplaced, against the $121,500,000 announced</t>
   </si>
   <si>
-    <t xml:space="preserve">19,143,072.00 -- inside, never on top</t>
+    <t xml:space="preserve">29,346,727.00 -- inside, never on top</t>
   </si>
   <si>
     <t xml:space="preserve">RHTP contracts OUTSIDE the RHT series (not extracted)</t>
@@ -1424,19 +1718,19 @@
     <t xml:space="preserve">rows distributed_to_hospital = Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
+    <t xml:space="preserve">17</t>
   </si>
   <si>
     <t xml:space="preserve">dollars distributed_to_hospital = Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">16,643,252.00</t>
+    <t xml:space="preserve">24,433,212.00</t>
   </si>
   <si>
     <t xml:space="preserve">distinct hospitals among them</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
+    <t xml:space="preserve">15</t>
   </si>
   <si>
     <t xml:space="preserve">round</t>
@@ -2347,7 +2641,7 @@
       <c r="S5"/>
       <c r="T5"/>
       <c r="U5" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V5"/>
       <c r="W5" t="s">
@@ -2357,10 +2651,10 @@
         <v>47</v>
       </c>
       <c r="Y5" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z5" t="s">
         <v>97</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>98</v>
       </c>
       <c r="AA5" t="s">
         <v>95</v>
@@ -2375,13 +2669,13 @@
         <v>62</v>
       </c>
       <c r="AE5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF5" t="s">
         <v>99</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AG5" t="s">
         <v>100</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>101</v>
       </c>
       <c r="AH5" t="s">
         <v>66</v>
@@ -2390,17 +2684,17 @@
         <v>46143</v>
       </c>
       <c r="AJ5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s">
         <v>44</v>
       </c>
       <c r="AL5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AM5"/>
       <c r="AN5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AO5" t="s">
         <v>69</v>
@@ -2419,7 +2713,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" t="n">
         <v>503000</v>
@@ -2431,7 +2725,7 @@
         <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
         <v>49</v>
@@ -2443,10 +2737,10 @@
         <v>50</v>
       </c>
       <c r="K6" t="s">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s">
         <v>106</v>
-      </c>
-      <c r="L6" t="s">
-        <v>107</v>
       </c>
       <c r="M6" t="s">
         <v>53</v>
@@ -2473,13 +2767,13 @@
         <v>47</v>
       </c>
       <c r="Y6" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z6" t="s">
         <v>108</v>
       </c>
-      <c r="Z6" t="s">
-        <v>109</v>
-      </c>
       <c r="AA6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB6" t="s">
         <v>60</v>
@@ -2494,10 +2788,10 @@
         <v>63</v>
       </c>
       <c r="AF6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG6" t="s">
         <v>110</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>111</v>
       </c>
       <c r="AH6" t="s">
         <v>66</v>
@@ -2506,17 +2800,17 @@
         <v>46143</v>
       </c>
       <c r="AJ6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK6" t="s">
         <v>44</v>
       </c>
       <c r="AL6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AM6"/>
       <c r="AN6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AO6" t="s">
         <v>69</v>
@@ -2535,7 +2829,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="n">
         <v>567350</v>
@@ -2547,7 +2841,7 @@
         <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H7" t="s">
         <v>49</v>
@@ -2559,10 +2853,10 @@
         <v>50</v>
       </c>
       <c r="K7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L7" t="s">
         <v>116</v>
-      </c>
-      <c r="L7" t="s">
-        <v>117</v>
       </c>
       <c r="M7" t="s">
         <v>53</v>
@@ -2579,7 +2873,7 @@
       <c r="S7"/>
       <c r="T7"/>
       <c r="U7" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V7"/>
       <c r="W7" t="s">
@@ -2589,13 +2883,13 @@
         <v>47</v>
       </c>
       <c r="Y7" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z7" t="s">
         <v>118</v>
       </c>
-      <c r="Z7" t="s">
-        <v>119</v>
-      </c>
       <c r="AA7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AB7" t="s">
         <v>60</v>
@@ -2610,10 +2904,10 @@
         <v>63</v>
       </c>
       <c r="AF7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG7" t="s">
         <v>120</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>121</v>
       </c>
       <c r="AH7" t="s">
         <v>66</v>
@@ -2622,17 +2916,17 @@
         <v>46174</v>
       </c>
       <c r="AJ7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AK7" t="s">
         <v>122</v>
       </c>
-      <c r="AK7" t="s">
-        <v>123</v>
-      </c>
       <c r="AL7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AM7"/>
       <c r="AN7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AO7" t="s">
         <v>69</v>
@@ -2651,7 +2945,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D8" t="n">
         <v>450000</v>
@@ -2663,7 +2957,7 @@
         <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H8" t="s">
         <v>49</v>
@@ -2675,10 +2969,10 @@
         <v>50</v>
       </c>
       <c r="K8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s">
         <v>127</v>
-      </c>
-      <c r="L8" t="s">
-        <v>128</v>
       </c>
       <c r="M8" t="s">
         <v>53</v>
@@ -2695,7 +2989,7 @@
       <c r="S8"/>
       <c r="T8"/>
       <c r="U8" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V8"/>
       <c r="W8" t="s">
@@ -2705,13 +2999,13 @@
         <v>47</v>
       </c>
       <c r="Y8" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z8" t="s">
         <v>129</v>
       </c>
-      <c r="Z8" t="s">
-        <v>130</v>
-      </c>
       <c r="AA8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB8" t="s">
         <v>60</v>
@@ -2726,10 +3020,10 @@
         <v>63</v>
       </c>
       <c r="AF8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG8" t="s">
         <v>131</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>132</v>
       </c>
       <c r="AH8" t="s">
         <v>66</v>
@@ -2738,17 +3032,17 @@
         <v>46174</v>
       </c>
       <c r="AJ8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK8" t="s">
         <v>133</v>
       </c>
-      <c r="AK8" t="s">
-        <v>134</v>
-      </c>
       <c r="AL8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM8"/>
       <c r="AN8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s">
         <v>69</v>
@@ -2767,7 +3061,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D9" t="n">
         <v>226930</v>
@@ -2779,7 +3073,7 @@
         <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H9" t="s">
         <v>49</v>
@@ -2791,10 +3085,10 @@
         <v>50</v>
       </c>
       <c r="K9" t="s">
+        <v>137</v>
+      </c>
+      <c r="L9" t="s">
         <v>138</v>
-      </c>
-      <c r="L9" t="s">
-        <v>139</v>
       </c>
       <c r="M9" t="s">
         <v>53</v>
@@ -2821,13 +3115,13 @@
         <v>47</v>
       </c>
       <c r="Y9" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z9" t="s">
         <v>140</v>
       </c>
-      <c r="Z9" t="s">
-        <v>141</v>
-      </c>
       <c r="AA9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB9" t="s">
         <v>60</v>
@@ -2843,7 +3137,7 @@
       </c>
       <c r="AF9"/>
       <c r="AG9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AH9" t="s">
         <v>66</v>
@@ -2859,10 +3153,10 @@
       </c>
       <c r="AL9"/>
       <c r="AM9" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN9" t="s">
         <v>143</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>144</v>
       </c>
       <c r="AO9" t="s">
         <v>69</v>
@@ -2881,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
         <v>130571</v>
@@ -2893,7 +3187,7 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
         <v>49</v>
@@ -2905,10 +3199,10 @@
         <v>50</v>
       </c>
       <c r="K10" t="s">
+        <v>145</v>
+      </c>
+      <c r="L10" t="s">
         <v>146</v>
-      </c>
-      <c r="L10" t="s">
-        <v>147</v>
       </c>
       <c r="M10" t="s">
         <v>53</v>
@@ -2935,13 +3229,13 @@
         <v>47</v>
       </c>
       <c r="Y10" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z10" t="s">
         <v>148</v>
       </c>
-      <c r="Z10" t="s">
-        <v>149</v>
-      </c>
       <c r="AA10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AB10" t="s">
         <v>60</v>
@@ -2957,7 +3251,7 @@
       </c>
       <c r="AF10"/>
       <c r="AG10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH10" t="s">
         <v>66</v>
@@ -2973,10 +3267,10 @@
       </c>
       <c r="AL10"/>
       <c r="AM10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AO10" t="s">
         <v>69</v>
@@ -2995,7 +3289,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
         <v>170816</v>
@@ -3007,7 +3301,7 @@
         <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H11" t="s">
         <v>49</v>
@@ -3019,10 +3313,10 @@
         <v>50</v>
       </c>
       <c r="K11" t="s">
+        <v>151</v>
+      </c>
+      <c r="L11" t="s">
         <v>152</v>
-      </c>
-      <c r="L11" t="s">
-        <v>153</v>
       </c>
       <c r="M11" t="s">
         <v>53</v>
@@ -3049,13 +3343,13 @@
         <v>47</v>
       </c>
       <c r="Y11" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z11" t="s">
         <v>154</v>
       </c>
-      <c r="Z11" t="s">
-        <v>155</v>
-      </c>
       <c r="AA11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AB11" t="s">
         <v>60</v>
@@ -3071,7 +3365,7 @@
       </c>
       <c r="AF11"/>
       <c r="AG11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AH11" t="s">
         <v>66</v>
@@ -3087,10 +3381,10 @@
       </c>
       <c r="AL11"/>
       <c r="AM11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s">
         <v>69</v>
@@ -3109,7 +3403,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>88800</v>
@@ -3121,7 +3415,7 @@
         <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H12" t="s">
         <v>49</v>
@@ -3133,10 +3427,10 @@
         <v>50</v>
       </c>
       <c r="K12" t="s">
+        <v>159</v>
+      </c>
+      <c r="L12" t="s">
         <v>160</v>
-      </c>
-      <c r="L12" t="s">
-        <v>161</v>
       </c>
       <c r="M12" t="s">
         <v>53</v>
@@ -3153,7 +3447,7 @@
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V12"/>
       <c r="W12" t="s">
@@ -3163,13 +3457,13 @@
         <v>47</v>
       </c>
       <c r="Y12" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z12" t="s">
         <v>162</v>
       </c>
-      <c r="Z12" t="s">
-        <v>163</v>
-      </c>
       <c r="AA12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="s">
         <v>60</v>
@@ -3181,13 +3475,13 @@
         <v>62</v>
       </c>
       <c r="AE12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF12" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG12" t="s">
         <v>164</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>165</v>
       </c>
       <c r="AH12" t="s">
         <v>66</v>
@@ -3202,11 +3496,11 @@
         <v>44</v>
       </c>
       <c r="AL12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AM12"/>
       <c r="AN12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AO12" t="s">
         <v>69</v>
@@ -3225,7 +3519,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D13" t="n">
         <v>425000</v>
@@ -3237,7 +3531,7 @@
         <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" t="s">
         <v>49</v>
@@ -3249,10 +3543,10 @@
         <v>50</v>
       </c>
       <c r="K13" t="s">
+        <v>168</v>
+      </c>
+      <c r="L13" t="s">
         <v>169</v>
-      </c>
-      <c r="L13" t="s">
-        <v>170</v>
       </c>
       <c r="M13" t="s">
         <v>53</v>
@@ -3269,7 +3563,7 @@
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V13"/>
       <c r="W13" t="s">
@@ -3279,13 +3573,13 @@
         <v>47</v>
       </c>
       <c r="Y13" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z13" t="s">
         <v>171</v>
       </c>
-      <c r="Z13" t="s">
-        <v>172</v>
-      </c>
       <c r="AA13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AB13" t="s">
         <v>60</v>
@@ -3300,10 +3594,10 @@
         <v>63</v>
       </c>
       <c r="AF13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG13" t="s">
         <v>173</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>174</v>
       </c>
       <c r="AH13" t="s">
         <v>66</v>
@@ -3312,17 +3606,17 @@
         <v>46174</v>
       </c>
       <c r="AJ13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK13" t="s">
         <v>175</v>
       </c>
-      <c r="AK13" t="s">
-        <v>176</v>
-      </c>
       <c r="AL13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AM13"/>
       <c r="AN13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s">
         <v>69</v>
@@ -3341,7 +3635,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
         <v>719085</v>
@@ -3353,7 +3647,7 @@
         <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H14" t="s">
         <v>49</v>
@@ -3365,10 +3659,10 @@
         <v>50</v>
       </c>
       <c r="K14" t="s">
+        <v>178</v>
+      </c>
+      <c r="L14" t="s">
         <v>179</v>
-      </c>
-      <c r="L14" t="s">
-        <v>180</v>
       </c>
       <c r="M14" t="s">
         <v>53</v>
@@ -3395,13 +3689,13 @@
         <v>47</v>
       </c>
       <c r="Y14" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z14" t="s">
         <v>181</v>
       </c>
-      <c r="Z14" t="s">
-        <v>182</v>
-      </c>
       <c r="AA14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB14" t="s">
         <v>60</v>
@@ -3416,10 +3710,10 @@
         <v>63</v>
       </c>
       <c r="AF14" t="s">
+        <v>182</v>
+      </c>
+      <c r="AG14" t="s">
         <v>183</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>184</v>
       </c>
       <c r="AH14" t="s">
         <v>66</v>
@@ -3434,11 +3728,11 @@
         <v>44</v>
       </c>
       <c r="AL14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AM14"/>
       <c r="AN14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s">
         <v>69</v>
@@ -3457,7 +3751,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D15" t="n">
         <v>133352</v>
@@ -3469,7 +3763,7 @@
         <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" t="s">
         <v>49</v>
@@ -3481,10 +3775,10 @@
         <v>50</v>
       </c>
       <c r="K15" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" t="s">
         <v>187</v>
-      </c>
-      <c r="L15" t="s">
-        <v>188</v>
       </c>
       <c r="M15" t="s">
         <v>53</v>
@@ -3501,10 +3795,10 @@
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15" t="s">
+        <v>188</v>
+      </c>
+      <c r="V15" t="s">
         <v>189</v>
-      </c>
-      <c r="V15" t="s">
-        <v>190</v>
       </c>
       <c r="W15" t="s">
         <v>57</v>
@@ -3513,13 +3807,13 @@
         <v>47</v>
       </c>
       <c r="Y15" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z15" t="s">
         <v>191</v>
       </c>
-      <c r="Z15" t="s">
-        <v>192</v>
-      </c>
       <c r="AA15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AB15" t="s">
         <v>60</v>
@@ -3531,11 +3825,11 @@
         <v>62</v>
       </c>
       <c r="AE15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF15"/>
       <c r="AG15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH15" t="s">
         <v>66</v>
@@ -3551,17 +3845,17 @@
       </c>
       <c r="AL15"/>
       <c r="AM15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AO15" t="s">
         <v>69</v>
       </c>
       <c r="AP15"/>
       <c r="AQ15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR15"/>
     </row>
@@ -3573,19 +3867,19 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D16" t="n">
         <v>467790</v>
       </c>
       <c r="E16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F16" t="s">
         <v>47</v>
       </c>
       <c r="G16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H16" t="s">
         <v>49</v>
@@ -3597,10 +3891,10 @@
         <v>50</v>
       </c>
       <c r="K16" t="s">
+        <v>199</v>
+      </c>
+      <c r="L16" t="s">
         <v>200</v>
-      </c>
-      <c r="L16" t="s">
-        <v>201</v>
       </c>
       <c r="M16" t="s">
         <v>53</v>
@@ -3617,7 +3911,7 @@
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V16"/>
       <c r="W16" t="s">
@@ -3627,13 +3921,13 @@
         <v>47</v>
       </c>
       <c r="Y16" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z16" t="s">
         <v>202</v>
       </c>
-      <c r="Z16" t="s">
-        <v>203</v>
-      </c>
       <c r="AA16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AB16" t="s">
         <v>60</v>
@@ -3645,11 +3939,11 @@
         <v>62</v>
       </c>
       <c r="AE16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF16"/>
       <c r="AG16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AH16" t="s">
         <v>66</v>
@@ -3665,19 +3959,19 @@
       </c>
       <c r="AL16"/>
       <c r="AM16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN16" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO16" t="s">
         <v>205</v>
       </c>
-      <c r="AO16" t="s">
+      <c r="AP16" t="s">
         <v>206</v>
       </c>
-      <c r="AP16" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR16"/>
     </row>
@@ -3689,7 +3983,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D17" t="n">
         <v>324000</v>
@@ -3701,7 +3995,7 @@
         <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H17" t="s">
         <v>49</v>
@@ -3713,10 +4007,10 @@
         <v>50</v>
       </c>
       <c r="K17" t="s">
+        <v>209</v>
+      </c>
+      <c r="L17" t="s">
         <v>210</v>
-      </c>
-      <c r="L17" t="s">
-        <v>211</v>
       </c>
       <c r="M17" t="s">
         <v>53</v>
@@ -3733,7 +4027,7 @@
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V17"/>
       <c r="W17" t="s">
@@ -3743,13 +4037,13 @@
         <v>47</v>
       </c>
       <c r="Y17" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z17" t="s">
         <v>212</v>
       </c>
-      <c r="Z17" t="s">
-        <v>213</v>
-      </c>
       <c r="AA17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB17" t="s">
         <v>60</v>
@@ -3761,13 +4055,13 @@
         <v>62</v>
       </c>
       <c r="AE17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF17" t="s">
         <v>99</v>
       </c>
-      <c r="AF17" t="s">
-        <v>100</v>
-      </c>
       <c r="AG17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AH17" t="s">
         <v>66</v>
@@ -3776,26 +4070,26 @@
         <v>46235</v>
       </c>
       <c r="AJ17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AK17" t="s">
         <v>44</v>
       </c>
       <c r="AL17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AM17"/>
       <c r="AN17" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO17" t="s">
         <v>205</v>
       </c>
-      <c r="AO17" t="s">
+      <c r="AP17" t="s">
         <v>206</v>
       </c>
-      <c r="AP17" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR17"/>
     </row>
@@ -3807,7 +4101,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D18" t="n">
         <v>370562</v>
@@ -3819,7 +4113,7 @@
         <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H18" t="s">
         <v>49</v>
@@ -3831,10 +4125,10 @@
         <v>50</v>
       </c>
       <c r="K18" t="s">
+        <v>217</v>
+      </c>
+      <c r="L18" t="s">
         <v>218</v>
-      </c>
-      <c r="L18" t="s">
-        <v>219</v>
       </c>
       <c r="M18" t="s">
         <v>53</v>
@@ -3851,10 +4145,10 @@
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18" t="s">
+        <v>188</v>
+      </c>
+      <c r="V18" t="s">
         <v>189</v>
-      </c>
-      <c r="V18" t="s">
-        <v>190</v>
       </c>
       <c r="W18" t="s">
         <v>57</v>
@@ -3863,13 +4157,13 @@
         <v>47</v>
       </c>
       <c r="Y18" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z18" t="s">
         <v>220</v>
       </c>
-      <c r="Z18" t="s">
-        <v>221</v>
-      </c>
       <c r="AA18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AB18" t="s">
         <v>60</v>
@@ -3881,11 +4175,11 @@
         <v>62</v>
       </c>
       <c r="AE18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF18"/>
       <c r="AG18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AH18" t="s">
         <v>66</v>
@@ -3894,26 +4188,26 @@
         <v>46235</v>
       </c>
       <c r="AJ18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AK18" t="s">
         <v>44</v>
       </c>
       <c r="AL18"/>
       <c r="AM18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN18" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO18" t="s">
         <v>205</v>
       </c>
-      <c r="AO18" t="s">
+      <c r="AP18" t="s">
         <v>206</v>
       </c>
-      <c r="AP18" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR18"/>
     </row>
@@ -3925,19 +4219,19 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D19" t="n">
         <v>145500</v>
       </c>
       <c r="E19" t="s">
+        <v>224</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" t="s">
         <v>225</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" t="s">
-        <v>226</v>
       </c>
       <c r="H19" t="s">
         <v>49</v>
@@ -3949,10 +4243,10 @@
         <v>50</v>
       </c>
       <c r="K19" t="s">
+        <v>226</v>
+      </c>
+      <c r="L19" t="s">
         <v>227</v>
-      </c>
-      <c r="L19" t="s">
-        <v>228</v>
       </c>
       <c r="M19" t="s">
         <v>53</v>
@@ -3969,23 +4263,23 @@
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V19"/>
       <c r="W19" t="s">
+        <v>228</v>
+      </c>
+      <c r="X19" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y19" t="s">
         <v>229</v>
       </c>
-      <c r="X19" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y19" t="s">
+      <c r="Z19" t="s">
         <v>230</v>
       </c>
-      <c r="Z19" t="s">
-        <v>231</v>
-      </c>
       <c r="AA19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AB19" t="s">
         <v>60</v>
@@ -3997,11 +4291,11 @@
         <v>62</v>
       </c>
       <c r="AE19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF19"/>
       <c r="AG19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AH19" t="s">
         <v>66</v>
@@ -4010,26 +4304,26 @@
         <v>46235</v>
       </c>
       <c r="AJ19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AK19" t="s">
         <v>44</v>
       </c>
       <c r="AL19"/>
       <c r="AM19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN19" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO19" t="s">
         <v>205</v>
       </c>
-      <c r="AO19" t="s">
+      <c r="AP19" t="s">
         <v>206</v>
       </c>
-      <c r="AP19" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR19"/>
     </row>
@@ -4041,7 +4335,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D20" t="n">
         <v>307228</v>
@@ -4053,7 +4347,7 @@
         <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H20" t="s">
         <v>49</v>
@@ -4065,10 +4359,10 @@
         <v>50</v>
       </c>
       <c r="K20" t="s">
+        <v>233</v>
+      </c>
+      <c r="L20" t="s">
         <v>234</v>
-      </c>
-      <c r="L20" t="s">
-        <v>235</v>
       </c>
       <c r="M20" t="s">
         <v>53</v>
@@ -4085,7 +4379,7 @@
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V20"/>
       <c r="W20" t="s">
@@ -4095,13 +4389,13 @@
         <v>47</v>
       </c>
       <c r="Y20" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z20" t="s">
         <v>236</v>
       </c>
-      <c r="Z20" t="s">
-        <v>237</v>
-      </c>
       <c r="AA20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB20" t="s">
         <v>60</v>
@@ -4113,13 +4407,13 @@
         <v>62</v>
       </c>
       <c r="AE20" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF20" t="s">
         <v>99</v>
       </c>
-      <c r="AF20" t="s">
-        <v>100</v>
-      </c>
       <c r="AG20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AH20" t="s">
         <v>66</v>
@@ -4128,24 +4422,24 @@
         <v>46204</v>
       </c>
       <c r="AJ20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AK20" t="s">
         <v>44</v>
       </c>
       <c r="AL20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AM20"/>
       <c r="AN20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO20" t="s">
         <v>69</v>
       </c>
       <c r="AP20"/>
       <c r="AQ20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR20"/>
     </row>
@@ -4157,7 +4451,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>449402</v>
@@ -4169,7 +4463,7 @@
         <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H21" t="s">
         <v>49</v>
@@ -4181,10 +4475,10 @@
         <v>50</v>
       </c>
       <c r="K21" t="s">
+        <v>240</v>
+      </c>
+      <c r="L21" t="s">
         <v>241</v>
-      </c>
-      <c r="L21" t="s">
-        <v>242</v>
       </c>
       <c r="M21" t="s">
         <v>53</v>
@@ -4211,13 +4505,13 @@
         <v>47</v>
       </c>
       <c r="Y21" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z21" t="s">
         <v>243</v>
       </c>
-      <c r="Z21" t="s">
-        <v>244</v>
-      </c>
       <c r="AA21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AB21" t="s">
         <v>60</v>
@@ -4232,10 +4526,10 @@
         <v>63</v>
       </c>
       <c r="AF21" t="s">
+        <v>244</v>
+      </c>
+      <c r="AG21" t="s">
         <v>245</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>246</v>
       </c>
       <c r="AH21" t="s">
         <v>66</v>
@@ -4244,24 +4538,24 @@
         <v>46235</v>
       </c>
       <c r="AJ21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK21" t="s">
         <v>44</v>
       </c>
       <c r="AL21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AM21"/>
       <c r="AN21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s">
         <v>69</v>
       </c>
       <c r="AP21"/>
       <c r="AQ21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR21"/>
     </row>
@@ -4297,10 +4591,10 @@
         <v>50</v>
       </c>
       <c r="K22" t="s">
+        <v>247</v>
+      </c>
+      <c r="L22" t="s">
         <v>248</v>
-      </c>
-      <c r="L22" t="s">
-        <v>249</v>
       </c>
       <c r="M22" t="s">
         <v>53</v>
@@ -4317,7 +4611,7 @@
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V22"/>
       <c r="W22" t="s">
@@ -4327,13 +4621,13 @@
         <v>47</v>
       </c>
       <c r="Y22" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z22" t="s">
         <v>250</v>
       </c>
-      <c r="Z22" t="s">
-        <v>251</v>
-      </c>
       <c r="AA22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AB22" t="s">
         <v>60</v>
@@ -4345,13 +4639,13 @@
         <v>62</v>
       </c>
       <c r="AE22" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF22" t="s">
         <v>99</v>
       </c>
-      <c r="AF22" t="s">
-        <v>100</v>
-      </c>
       <c r="AG22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AH22" t="s">
         <v>66</v>
@@ -4360,24 +4654,24 @@
         <v>46204</v>
       </c>
       <c r="AJ22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s">
         <v>44</v>
       </c>
       <c r="AL22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AM22"/>
       <c r="AN22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO22" t="s">
         <v>69</v>
       </c>
       <c r="AP22"/>
       <c r="AQ22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR22"/>
     </row>
@@ -4389,19 +4683,19 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D23" t="n">
         <v>38000</v>
       </c>
       <c r="E23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F23" t="s">
         <v>49</v>
       </c>
       <c r="G23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H23" t="s">
         <v>49</v>
@@ -4413,10 +4707,10 @@
         <v>50</v>
       </c>
       <c r="K23" t="s">
+        <v>254</v>
+      </c>
+      <c r="L23" t="s">
         <v>255</v>
-      </c>
-      <c r="L23" t="s">
-        <v>256</v>
       </c>
       <c r="M23" t="s">
         <v>53</v>
@@ -4428,20 +4722,20 @@
         <v>55</v>
       </c>
       <c r="P23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23"/>
       <c r="T23" t="s">
+        <v>257</v>
+      </c>
+      <c r="U23" t="s">
         <v>258</v>
-      </c>
-      <c r="U23" t="s">
-        <v>96</v>
       </c>
       <c r="V23"/>
       <c r="W23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X23" t="s">
         <v>49</v>
@@ -4453,7 +4747,7 @@
         <v>260</v>
       </c>
       <c r="AA23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AB23" t="s">
         <v>60</v>
@@ -4465,7 +4759,7 @@
         <v>62</v>
       </c>
       <c r="AE23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF23"/>
       <c r="AG23" t="s">
@@ -4485,19 +4779,19 @@
       </c>
       <c r="AL23"/>
       <c r="AM23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN23" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO23" t="s">
         <v>205</v>
       </c>
-      <c r="AO23" t="s">
+      <c r="AP23" t="s">
         <v>206</v>
       </c>
-      <c r="AP23" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR23"/>
     </row>
@@ -4515,7 +4809,7 @@
         <v>181600</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F24" t="s">
         <v>49</v>
@@ -4561,7 +4855,7 @@
       </c>
       <c r="V24"/>
       <c r="W24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X24" t="s">
         <v>49</v>
@@ -4605,19 +4899,19 @@
       </c>
       <c r="AL24"/>
       <c r="AM24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN24" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO24" t="s">
         <v>205</v>
       </c>
-      <c r="AO24" t="s">
+      <c r="AP24" t="s">
         <v>206</v>
       </c>
-      <c r="AP24" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR24"/>
     </row>
@@ -4629,13 +4923,13 @@
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D25" t="n">
         <v>103700</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F25" t="s">
         <v>49</v>
@@ -4677,11 +4971,11 @@
         <v>278</v>
       </c>
       <c r="U25" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="V25"/>
       <c r="W25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X25" t="s">
         <v>49</v>
@@ -4705,7 +4999,7 @@
         <v>62</v>
       </c>
       <c r="AE25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF25"/>
       <c r="AG25" t="s">
@@ -4725,19 +5019,19 @@
       </c>
       <c r="AL25"/>
       <c r="AM25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN25" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO25" t="s">
         <v>205</v>
       </c>
-      <c r="AO25" t="s">
+      <c r="AP25" t="s">
         <v>206</v>
       </c>
-      <c r="AP25" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR25"/>
     </row>
@@ -4755,7 +5049,7 @@
         <v>248000</v>
       </c>
       <c r="E26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F26" t="s">
         <v>49</v>
@@ -4793,11 +5087,11 @@
       <c r="S26"/>
       <c r="T26"/>
       <c r="U26" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V26"/>
       <c r="W26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X26" t="s">
         <v>49</v>
@@ -4821,7 +5115,7 @@
         <v>62</v>
       </c>
       <c r="AE26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF26"/>
       <c r="AG26" t="s">
@@ -4841,19 +5135,19 @@
       </c>
       <c r="AL26"/>
       <c r="AM26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN26" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO26" t="s">
         <v>205</v>
       </c>
-      <c r="AO26" t="s">
+      <c r="AP26" t="s">
         <v>206</v>
       </c>
-      <c r="AP26" t="s">
-        <v>207</v>
-      </c>
       <c r="AQ26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR26"/>
     </row>
@@ -4937,7 +5231,7 @@
         <v>62</v>
       </c>
       <c r="AE27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF27" t="s">
         <v>297</v>
@@ -4969,7 +5263,7 @@
       </c>
       <c r="AP27"/>
       <c r="AQ27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR27"/>
     </row>
@@ -4987,7 +5281,7 @@
         <v>1258349</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F28" t="s">
         <v>49</v>
@@ -5025,11 +5319,11 @@
       <c r="S28"/>
       <c r="T28"/>
       <c r="U28" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V28"/>
       <c r="W28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X28" t="s">
         <v>49</v>
@@ -5053,7 +5347,7 @@
         <v>62</v>
       </c>
       <c r="AE28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF28"/>
       <c r="AG28" t="s">
@@ -5073,16 +5367,16 @@
       </c>
       <c r="AL28"/>
       <c r="AM28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN28" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO28" t="s">
         <v>205</v>
       </c>
-      <c r="AO28" t="s">
+      <c r="AP28" t="s">
         <v>206</v>
-      </c>
-      <c r="AP28" t="s">
-        <v>207</v>
       </c>
       <c r="AQ28" t="s">
         <v>310</v>
@@ -5109,7 +5403,7 @@
         <v>47</v>
       </c>
       <c r="G29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H29" t="s">
         <v>49</v>
@@ -5141,10 +5435,10 @@
       <c r="S29"/>
       <c r="T29"/>
       <c r="U29" t="s">
+        <v>188</v>
+      </c>
+      <c r="V29" t="s">
         <v>189</v>
-      </c>
-      <c r="V29" t="s">
-        <v>190</v>
       </c>
       <c r="W29" t="s">
         <v>57</v>
@@ -5171,7 +5465,7 @@
         <v>62</v>
       </c>
       <c r="AE29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF29"/>
       <c r="AG29" t="s">
@@ -5191,10 +5485,10 @@
       </c>
       <c r="AL29"/>
       <c r="AM29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO29" t="s">
         <v>69</v>
@@ -5219,7 +5513,7 @@
         <v>418563</v>
       </c>
       <c r="E30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F30" t="s">
         <v>49</v>
@@ -5261,11 +5555,11 @@
         <v>322</v>
       </c>
       <c r="U30" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="V30"/>
       <c r="W30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X30" t="s">
         <v>49</v>
@@ -5289,7 +5583,7 @@
         <v>62</v>
       </c>
       <c r="AE30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF30"/>
       <c r="AG30" t="s">
@@ -5309,16 +5603,16 @@
       </c>
       <c r="AL30"/>
       <c r="AM30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN30" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO30" t="s">
         <v>205</v>
       </c>
-      <c r="AO30" t="s">
+      <c r="AP30" t="s">
         <v>206</v>
-      </c>
-      <c r="AP30" t="s">
-        <v>207</v>
       </c>
       <c r="AQ30" t="s">
         <v>310</v>
@@ -5339,13 +5633,13 @@
         <v>5442000</v>
       </c>
       <c r="E31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F31" t="s">
         <v>49</v>
       </c>
       <c r="G31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H31" t="s">
         <v>49</v>
@@ -5379,11 +5673,11 @@
         <v>330</v>
       </c>
       <c r="U31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V31"/>
       <c r="W31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X31" t="s">
         <v>49</v>
@@ -5427,16 +5721,16 @@
       </c>
       <c r="AL31"/>
       <c r="AM31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN31" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO31" t="s">
         <v>205</v>
       </c>
-      <c r="AO31" t="s">
+      <c r="AP31" t="s">
         <v>206</v>
-      </c>
-      <c r="AP31" t="s">
-        <v>207</v>
       </c>
       <c r="AQ31" t="s">
         <v>310</v>
@@ -5459,7 +5753,7 @@
         <v>2704989</v>
       </c>
       <c r="E32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F32" t="s">
         <v>49</v>
@@ -5501,11 +5795,11 @@
         <v>341</v>
       </c>
       <c r="U32" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="V32"/>
       <c r="W32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X32" t="s">
         <v>49</v>
@@ -5529,7 +5823,7 @@
         <v>62</v>
       </c>
       <c r="AE32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF32"/>
       <c r="AG32" t="s">
@@ -5549,16 +5843,16 @@
       </c>
       <c r="AL32"/>
       <c r="AM32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN32" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO32" t="s">
         <v>205</v>
       </c>
-      <c r="AO32" t="s">
+      <c r="AP32" t="s">
         <v>206</v>
-      </c>
-      <c r="AP32" t="s">
-        <v>207</v>
       </c>
       <c r="AQ32" t="s">
         <v>310</v>
@@ -5579,7 +5873,7 @@
         <v>2699907</v>
       </c>
       <c r="E33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F33" t="s">
         <v>49</v>
@@ -5625,7 +5919,7 @@
       </c>
       <c r="V33"/>
       <c r="W33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X33" t="s">
         <v>49</v>
@@ -5669,16 +5963,16 @@
       </c>
       <c r="AL33"/>
       <c r="AM33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN33" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO33" t="s">
         <v>205</v>
       </c>
-      <c r="AO33" t="s">
+      <c r="AP33" t="s">
         <v>206</v>
-      </c>
-      <c r="AP33" t="s">
-        <v>207</v>
       </c>
       <c r="AQ33" t="s">
         <v>310</v>
@@ -5699,13 +5993,13 @@
         <v>1565000</v>
       </c>
       <c r="E34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F34" t="s">
         <v>49</v>
       </c>
       <c r="G34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H34" t="s">
         <v>49</v>
@@ -5739,11 +6033,11 @@
         <v>359</v>
       </c>
       <c r="U34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V34"/>
       <c r="W34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X34" t="s">
         <v>49</v>
@@ -5787,16 +6081,16 @@
       </c>
       <c r="AL34"/>
       <c r="AM34" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN34" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO34" t="s">
         <v>205</v>
       </c>
-      <c r="AO34" t="s">
+      <c r="AP34" t="s">
         <v>206</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>207</v>
       </c>
       <c r="AQ34" t="s">
         <v>310</v>
@@ -5813,19 +6107,19 @@
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D35" t="n">
         <v>77432</v>
       </c>
       <c r="E35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F35" t="s">
         <v>49</v>
       </c>
       <c r="G35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H35" t="s">
         <v>49</v>
@@ -5852,20 +6146,20 @@
         <v>55</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q35"/>
       <c r="R35"/>
       <c r="S35"/>
       <c r="T35" t="s">
+        <v>257</v>
+      </c>
+      <c r="U35" t="s">
         <v>258</v>
-      </c>
-      <c r="U35" t="s">
-        <v>96</v>
       </c>
       <c r="V35"/>
       <c r="W35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X35" t="s">
         <v>49</v>
@@ -5889,7 +6183,7 @@
         <v>62</v>
       </c>
       <c r="AE35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF35"/>
       <c r="AG35" t="s">
@@ -5909,7 +6203,7 @@
       </c>
       <c r="AL35"/>
       <c r="AM35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN35" t="s">
         <v>368</v>
@@ -5939,7 +6233,7 @@
         <v>175000</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F36" t="s">
         <v>49</v>
@@ -5981,11 +6275,11 @@
         <v>341</v>
       </c>
       <c r="U36" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="V36"/>
       <c r="W36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X36" t="s">
         <v>49</v>
@@ -6009,7 +6303,7 @@
         <v>62</v>
       </c>
       <c r="AE36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF36"/>
       <c r="AG36" t="s">
@@ -6029,7 +6323,7 @@
       </c>
       <c r="AL36"/>
       <c r="AM36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN36" t="s">
         <v>368</v>
@@ -6097,10 +6391,10 @@
       <c r="S37"/>
       <c r="T37"/>
       <c r="U37" t="s">
+        <v>188</v>
+      </c>
+      <c r="V37" t="s">
         <v>189</v>
-      </c>
-      <c r="V37" t="s">
-        <v>190</v>
       </c>
       <c r="W37" t="s">
         <v>57</v>
@@ -6127,7 +6421,7 @@
         <v>62</v>
       </c>
       <c r="AE37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF37"/>
       <c r="AG37" t="s">
@@ -6147,7 +6441,7 @@
       </c>
       <c r="AL37"/>
       <c r="AM37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN37" t="s">
         <v>382</v>
@@ -6177,7 +6471,7 @@
         <v>1585212</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F38" t="s">
         <v>49</v>
@@ -6223,7 +6517,7 @@
       </c>
       <c r="V38"/>
       <c r="W38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X38" t="s">
         <v>49</v>
@@ -6267,7 +6561,7 @@
       </c>
       <c r="AL38"/>
       <c r="AM38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN38" t="s">
         <v>393</v>
@@ -6335,7 +6629,7 @@
       <c r="S39"/>
       <c r="T39"/>
       <c r="U39" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="V39"/>
       <c r="W39" t="s">
@@ -6363,10 +6657,10 @@
         <v>62</v>
       </c>
       <c r="AE39" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF39" t="s">
         <v>99</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>100</v>
       </c>
       <c r="AG39" t="s">
         <v>400</v>
@@ -6384,7 +6678,7 @@
         <v>44</v>
       </c>
       <c r="AL39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AM39"/>
       <c r="AN39" t="s">
@@ -6421,7 +6715,7 @@
         <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H40" t="s">
         <v>49</v>
@@ -6453,10 +6747,10 @@
       <c r="S40"/>
       <c r="T40"/>
       <c r="U40" t="s">
+        <v>188</v>
+      </c>
+      <c r="V40" t="s">
         <v>189</v>
-      </c>
-      <c r="V40" t="s">
-        <v>190</v>
       </c>
       <c r="W40" t="s">
         <v>57</v>
@@ -6483,7 +6777,7 @@
         <v>62</v>
       </c>
       <c r="AE40" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF40"/>
       <c r="AG40" t="s">
@@ -6503,7 +6797,7 @@
       </c>
       <c r="AL40"/>
       <c r="AM40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN40" t="s">
         <v>368</v>
@@ -6539,7 +6833,7 @@
         <v>47</v>
       </c>
       <c r="G41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H41" t="s">
         <v>49</v>
@@ -6571,10 +6865,10 @@
       <c r="S41"/>
       <c r="T41"/>
       <c r="U41" t="s">
+        <v>188</v>
+      </c>
+      <c r="V41" t="s">
         <v>189</v>
-      </c>
-      <c r="V41" t="s">
-        <v>190</v>
       </c>
       <c r="W41" t="s">
         <v>57</v>
@@ -6601,7 +6895,7 @@
         <v>62</v>
       </c>
       <c r="AE41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF41"/>
       <c r="AG41" t="s">
@@ -6614,14 +6908,14 @@
         <v>46054</v>
       </c>
       <c r="AJ41" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AK41" t="s">
         <v>44</v>
       </c>
       <c r="AL41"/>
       <c r="AM41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AN41" t="s">
         <v>415</v>
@@ -6689,10 +6983,10 @@
       <c r="S42"/>
       <c r="T42"/>
       <c r="U42" t="s">
+        <v>188</v>
+      </c>
+      <c r="V42" t="s">
         <v>189</v>
-      </c>
-      <c r="V42" t="s">
-        <v>190</v>
       </c>
       <c r="W42" t="s">
         <v>57</v>
@@ -6719,10 +7013,10 @@
         <v>62</v>
       </c>
       <c r="AE42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG42" t="s">
         <v>422</v>
@@ -6740,7 +7034,7 @@
         <v>44</v>
       </c>
       <c r="AL42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AM42"/>
       <c r="AN42" t="s">
@@ -6756,6 +7050,1430 @@
         <v>310</v>
       </c>
       <c r="AR42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>424</v>
+      </c>
+      <c r="D43" t="n">
+        <v>485550</v>
+      </c>
+      <c r="E43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G43" t="s">
+        <v>425</v>
+      </c>
+      <c r="H43" t="s">
+        <v>49</v>
+      </c>
+      <c r="I43" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43" t="s">
+        <v>50</v>
+      </c>
+      <c r="K43" t="s">
+        <v>426</v>
+      </c>
+      <c r="L43" t="s">
+        <v>427</v>
+      </c>
+      <c r="M43" t="s">
+        <v>53</v>
+      </c>
+      <c r="N43" t="s">
+        <v>54</v>
+      </c>
+      <c r="O43" t="s">
+        <v>55</v>
+      </c>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+      <c r="S43"/>
+      <c r="T43"/>
+      <c r="U43" t="s">
+        <v>188</v>
+      </c>
+      <c r="V43" t="s">
+        <v>189</v>
+      </c>
+      <c r="W43" t="s">
+        <v>57</v>
+      </c>
+      <c r="X43" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>428</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>429</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>427</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF43"/>
+      <c r="AG43" t="s">
+        <v>430</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI43" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>431</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL43"/>
+      <c r="AM43" t="s">
+        <v>432</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO43" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP43" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ43" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>434</v>
+      </c>
+      <c r="D44" t="n">
+        <v>134442</v>
+      </c>
+      <c r="E44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" t="s">
+        <v>49</v>
+      </c>
+      <c r="J44" t="s">
+        <v>50</v>
+      </c>
+      <c r="K44" t="s">
+        <v>435</v>
+      </c>
+      <c r="L44" t="s">
+        <v>436</v>
+      </c>
+      <c r="M44" t="s">
+        <v>53</v>
+      </c>
+      <c r="N44" t="s">
+        <v>54</v>
+      </c>
+      <c r="O44" t="s">
+        <v>55</v>
+      </c>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+      <c r="S44"/>
+      <c r="T44"/>
+      <c r="U44" t="s">
+        <v>188</v>
+      </c>
+      <c r="V44" t="s">
+        <v>189</v>
+      </c>
+      <c r="W44" t="s">
+        <v>57</v>
+      </c>
+      <c r="X44" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>437</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>438</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>436</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF44"/>
+      <c r="AG44" t="s">
+        <v>439</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI44" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL44"/>
+      <c r="AM44" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>440</v>
+      </c>
+      <c r="AO44" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP44" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ44" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="s">
+        <v>441</v>
+      </c>
+      <c r="D45" t="n">
+        <v>131460</v>
+      </c>
+      <c r="E45" t="s">
+        <v>224</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" t="s">
+        <v>442</v>
+      </c>
+      <c r="H45" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" t="s">
+        <v>49</v>
+      </c>
+      <c r="J45" t="s">
+        <v>50</v>
+      </c>
+      <c r="K45" t="s">
+        <v>443</v>
+      </c>
+      <c r="L45" t="s">
+        <v>444</v>
+      </c>
+      <c r="M45" t="s">
+        <v>53</v>
+      </c>
+      <c r="N45" t="s">
+        <v>54</v>
+      </c>
+      <c r="O45" t="s">
+        <v>55</v>
+      </c>
+      <c r="P45" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q45"/>
+      <c r="R45"/>
+      <c r="S45"/>
+      <c r="T45" t="s">
+        <v>446</v>
+      </c>
+      <c r="U45" t="s">
+        <v>188</v>
+      </c>
+      <c r="V45"/>
+      <c r="W45" t="s">
+        <v>228</v>
+      </c>
+      <c r="X45" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>447</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>448</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>444</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>449</v>
+      </c>
+      <c r="AF45"/>
+      <c r="AG45" t="s">
+        <v>450</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI45" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>451</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL45"/>
+      <c r="AM45" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>368</v>
+      </c>
+      <c r="AO45" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP45" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ45" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR45" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="s">
+        <v>452</v>
+      </c>
+      <c r="D46" t="n">
+        <v>119230</v>
+      </c>
+      <c r="E46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46" t="s">
+        <v>442</v>
+      </c>
+      <c r="H46" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" t="s">
+        <v>49</v>
+      </c>
+      <c r="J46" t="s">
+        <v>50</v>
+      </c>
+      <c r="K46" t="s">
+        <v>453</v>
+      </c>
+      <c r="L46" t="s">
+        <v>454</v>
+      </c>
+      <c r="M46" t="s">
+        <v>53</v>
+      </c>
+      <c r="N46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O46" t="s">
+        <v>55</v>
+      </c>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46" t="s">
+        <v>188</v>
+      </c>
+      <c r="V46" t="s">
+        <v>189</v>
+      </c>
+      <c r="W46" t="s">
+        <v>57</v>
+      </c>
+      <c r="X46" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>455</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>454</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF46"/>
+      <c r="AG46" t="s">
+        <v>457</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI46" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>451</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL46"/>
+      <c r="AM46" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>458</v>
+      </c>
+      <c r="AO46" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP46" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ46" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>459</v>
+      </c>
+      <c r="D47" t="n">
+        <v>64281</v>
+      </c>
+      <c r="E47" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G47" t="s">
+        <v>460</v>
+      </c>
+      <c r="H47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" t="s">
+        <v>49</v>
+      </c>
+      <c r="J47" t="s">
+        <v>50</v>
+      </c>
+      <c r="K47" t="s">
+        <v>461</v>
+      </c>
+      <c r="L47" t="s">
+        <v>462</v>
+      </c>
+      <c r="M47" t="s">
+        <v>53</v>
+      </c>
+      <c r="N47" t="s">
+        <v>54</v>
+      </c>
+      <c r="O47" t="s">
+        <v>55</v>
+      </c>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+      <c r="U47" t="s">
+        <v>188</v>
+      </c>
+      <c r="V47" t="s">
+        <v>189</v>
+      </c>
+      <c r="W47" t="s">
+        <v>57</v>
+      </c>
+      <c r="X47" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>462</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF47"/>
+      <c r="AG47" t="s">
+        <v>465</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI47" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>466</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL47"/>
+      <c r="AM47" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>467</v>
+      </c>
+      <c r="AO47" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP47" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ47" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>468</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6361000</v>
+      </c>
+      <c r="E48" t="s">
+        <v>224</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" t="s">
+        <v>216</v>
+      </c>
+      <c r="H48" t="s">
+        <v>49</v>
+      </c>
+      <c r="I48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J48" t="s">
+        <v>50</v>
+      </c>
+      <c r="K48" t="s">
+        <v>469</v>
+      </c>
+      <c r="L48" t="s">
+        <v>470</v>
+      </c>
+      <c r="M48" t="s">
+        <v>53</v>
+      </c>
+      <c r="N48" t="s">
+        <v>54</v>
+      </c>
+      <c r="O48" t="s">
+        <v>55</v>
+      </c>
+      <c r="P48" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q48"/>
+      <c r="R48"/>
+      <c r="S48"/>
+      <c r="T48" t="s">
+        <v>472</v>
+      </c>
+      <c r="U48" t="s">
+        <v>188</v>
+      </c>
+      <c r="V48"/>
+      <c r="W48" t="s">
+        <v>228</v>
+      </c>
+      <c r="X48" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>473</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>474</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>470</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>449</v>
+      </c>
+      <c r="AF48"/>
+      <c r="AG48" t="s">
+        <v>475</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI48" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>222</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL48"/>
+      <c r="AM48" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO48" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP48" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ48" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR48" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>476</v>
+      </c>
+      <c r="D49" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E49" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G49" t="s">
+        <v>216</v>
+      </c>
+      <c r="H49" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J49" t="s">
+        <v>50</v>
+      </c>
+      <c r="K49" t="s">
+        <v>477</v>
+      </c>
+      <c r="L49" t="s">
+        <v>478</v>
+      </c>
+      <c r="M49" t="s">
+        <v>53</v>
+      </c>
+      <c r="N49" t="s">
+        <v>54</v>
+      </c>
+      <c r="O49" t="s">
+        <v>55</v>
+      </c>
+      <c r="P49"/>
+      <c r="Q49"/>
+      <c r="R49"/>
+      <c r="S49"/>
+      <c r="T49"/>
+      <c r="U49" t="s">
+        <v>188</v>
+      </c>
+      <c r="V49" t="s">
+        <v>189</v>
+      </c>
+      <c r="W49" t="s">
+        <v>57</v>
+      </c>
+      <c r="X49" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>479</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>480</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF49"/>
+      <c r="AG49" t="s">
+        <v>481</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI49" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>222</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL49"/>
+      <c r="AM49" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO49" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP49" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ49" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>482</v>
+      </c>
+      <c r="D50" t="n">
+        <v>18650</v>
+      </c>
+      <c r="E50" t="s">
+        <v>82</v>
+      </c>
+      <c r="F50" t="s">
+        <v>47</v>
+      </c>
+      <c r="G50" t="s">
+        <v>483</v>
+      </c>
+      <c r="H50" t="s">
+        <v>49</v>
+      </c>
+      <c r="I50" t="s">
+        <v>49</v>
+      </c>
+      <c r="J50" t="s">
+        <v>50</v>
+      </c>
+      <c r="K50" t="s">
+        <v>484</v>
+      </c>
+      <c r="L50" t="s">
+        <v>485</v>
+      </c>
+      <c r="M50" t="s">
+        <v>53</v>
+      </c>
+      <c r="N50" t="s">
+        <v>54</v>
+      </c>
+      <c r="O50" t="s">
+        <v>55</v>
+      </c>
+      <c r="P50"/>
+      <c r="Q50"/>
+      <c r="R50"/>
+      <c r="S50"/>
+      <c r="T50"/>
+      <c r="U50" t="s">
+        <v>188</v>
+      </c>
+      <c r="V50" t="s">
+        <v>189</v>
+      </c>
+      <c r="W50" t="s">
+        <v>57</v>
+      </c>
+      <c r="X50" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>486</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>487</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>485</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF50"/>
+      <c r="AG50" t="s">
+        <v>488</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI50" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>489</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL50"/>
+      <c r="AM50" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>490</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR50"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>491</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1297500</v>
+      </c>
+      <c r="E51" t="s">
+        <v>224</v>
+      </c>
+      <c r="F51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G51" t="s">
+        <v>136</v>
+      </c>
+      <c r="H51" t="s">
+        <v>49</v>
+      </c>
+      <c r="I51" t="s">
+        <v>49</v>
+      </c>
+      <c r="J51" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" t="s">
+        <v>492</v>
+      </c>
+      <c r="L51" t="s">
+        <v>493</v>
+      </c>
+      <c r="M51" t="s">
+        <v>53</v>
+      </c>
+      <c r="N51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O51" t="s">
+        <v>55</v>
+      </c>
+      <c r="P51" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q51"/>
+      <c r="R51"/>
+      <c r="S51"/>
+      <c r="T51" t="s">
+        <v>495</v>
+      </c>
+      <c r="U51" t="s">
+        <v>188</v>
+      </c>
+      <c r="V51"/>
+      <c r="W51" t="s">
+        <v>228</v>
+      </c>
+      <c r="X51" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>496</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>497</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>493</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>449</v>
+      </c>
+      <c r="AF51"/>
+      <c r="AG51" t="s">
+        <v>498</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI51" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL51"/>
+      <c r="AM51" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO51" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" t="n">
+        <v>194685</v>
+      </c>
+      <c r="E52" t="s">
+        <v>197</v>
+      </c>
+      <c r="F52" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52" t="s">
+        <v>198</v>
+      </c>
+      <c r="H52" t="s">
+        <v>49</v>
+      </c>
+      <c r="I52" t="s">
+        <v>49</v>
+      </c>
+      <c r="J52" t="s">
+        <v>50</v>
+      </c>
+      <c r="K52" t="s">
+        <v>499</v>
+      </c>
+      <c r="L52" t="s">
+        <v>500</v>
+      </c>
+      <c r="M52" t="s">
+        <v>53</v>
+      </c>
+      <c r="N52" t="s">
+        <v>54</v>
+      </c>
+      <c r="O52" t="s">
+        <v>55</v>
+      </c>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="R52"/>
+      <c r="S52"/>
+      <c r="T52"/>
+      <c r="U52" t="s">
+        <v>56</v>
+      </c>
+      <c r="V52"/>
+      <c r="W52" t="s">
+        <v>57</v>
+      </c>
+      <c r="X52" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>501</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>502</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>500</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF52"/>
+      <c r="AG52" t="s">
+        <v>503</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI52" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL52"/>
+      <c r="AM52" t="s">
+        <v>504</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>368</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="s">
+        <v>505</v>
+      </c>
+      <c r="D53" t="n">
+        <v>459017</v>
+      </c>
+      <c r="E53" t="s">
+        <v>82</v>
+      </c>
+      <c r="F53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G53" t="s">
+        <v>506</v>
+      </c>
+      <c r="H53" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" t="s">
+        <v>49</v>
+      </c>
+      <c r="J53" t="s">
+        <v>50</v>
+      </c>
+      <c r="K53" t="s">
+        <v>507</v>
+      </c>
+      <c r="L53" t="s">
+        <v>508</v>
+      </c>
+      <c r="M53" t="s">
+        <v>53</v>
+      </c>
+      <c r="N53" t="s">
+        <v>54</v>
+      </c>
+      <c r="O53" t="s">
+        <v>55</v>
+      </c>
+      <c r="P53"/>
+      <c r="Q53"/>
+      <c r="R53"/>
+      <c r="S53"/>
+      <c r="T53"/>
+      <c r="U53" t="s">
+        <v>188</v>
+      </c>
+      <c r="V53" t="s">
+        <v>189</v>
+      </c>
+      <c r="W53" t="s">
+        <v>57</v>
+      </c>
+      <c r="X53" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>509</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>510</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>508</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF53"/>
+      <c r="AG53" t="s">
+        <v>511</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI53" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>512</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL53"/>
+      <c r="AM53" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>513</v>
+      </c>
+      <c r="AO53" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP53" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR53"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="s">
+        <v>514</v>
+      </c>
+      <c r="D54" t="n">
+        <v>37840</v>
+      </c>
+      <c r="E54" t="s">
+        <v>515</v>
+      </c>
+      <c r="F54" t="s">
+        <v>47</v>
+      </c>
+      <c r="G54" t="s">
+        <v>136</v>
+      </c>
+      <c r="H54" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" t="s">
+        <v>49</v>
+      </c>
+      <c r="J54" t="s">
+        <v>50</v>
+      </c>
+      <c r="K54" t="s">
+        <v>516</v>
+      </c>
+      <c r="L54" t="s">
+        <v>517</v>
+      </c>
+      <c r="M54" t="s">
+        <v>53</v>
+      </c>
+      <c r="N54" t="s">
+        <v>54</v>
+      </c>
+      <c r="O54" t="s">
+        <v>55</v>
+      </c>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+      <c r="S54"/>
+      <c r="T54"/>
+      <c r="U54" t="s">
+        <v>56</v>
+      </c>
+      <c r="V54"/>
+      <c r="W54" t="s">
+        <v>57</v>
+      </c>
+      <c r="X54" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>518</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>519</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>517</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF54"/>
+      <c r="AG54" t="s">
+        <v>520</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI54" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL54"/>
+      <c r="AM54" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>521</v>
+      </c>
+      <c r="AO54" t="s">
+        <v>369</v>
+      </c>
+      <c r="AP54" t="s">
+        <v>370</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6770,218 +8488,218 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>424</v>
+        <v>522</v>
       </c>
       <c r="B1" t="s">
-        <v>425</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>426</v>
+        <v>524</v>
       </c>
       <c r="B2" t="s">
-        <v>427</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>428</v>
+        <v>526</v>
       </c>
       <c r="B3" t="s">
-        <v>429</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>430</v>
+        <v>528</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>432</v>
+        <v>530</v>
       </c>
       <c r="B5" t="s">
-        <v>433</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>434</v>
+        <v>532</v>
       </c>
       <c r="B6" t="s">
-        <v>435</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="B7" t="s">
-        <v>437</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>438</v>
+        <v>536</v>
       </c>
       <c r="B8" t="s">
-        <v>439</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>440</v>
+        <v>538</v>
       </c>
       <c r="B9" t="s">
-        <v>433</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>441</v>
+        <v>539</v>
       </c>
       <c r="B10" t="s">
-        <v>442</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>443</v>
+        <v>541</v>
       </c>
       <c r="B11" t="s">
-        <v>444</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>445</v>
+        <v>543</v>
       </c>
       <c r="B12" t="s">
-        <v>446</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>447</v>
+        <v>545</v>
       </c>
       <c r="B13" t="s">
-        <v>448</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>449</v>
+        <v>547</v>
       </c>
       <c r="B14" t="s">
-        <v>450</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>451</v>
+        <v>549</v>
       </c>
       <c r="B15" t="s">
-        <v>433</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>452</v>
+        <v>550</v>
       </c>
       <c r="B16" t="s">
-        <v>453</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>454</v>
+        <v>552</v>
       </c>
       <c r="B17" t="s">
-        <v>455</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>456</v>
+        <v>554</v>
       </c>
       <c r="B18" t="s">
-        <v>457</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>458</v>
+        <v>556</v>
       </c>
       <c r="B19" t="s">
-        <v>433</v>
+        <v>531</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>459</v>
+        <v>557</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>461</v>
+        <v>559</v>
       </c>
       <c r="B21" t="s">
-        <v>462</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>463</v>
+        <v>561</v>
       </c>
       <c r="B22" t="s">
-        <v>464</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>465</v>
+        <v>563</v>
       </c>
       <c r="B23" t="s">
-        <v>466</v>
+        <v>564</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>467</v>
+        <v>565</v>
       </c>
       <c r="B24" t="s">
-        <v>433</v>
+        <v>531</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>468</v>
+        <v>566</v>
       </c>
       <c r="B25" t="s">
-        <v>469</v>
+        <v>567</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>470</v>
+        <v>568</v>
       </c>
       <c r="B26" t="s">
-        <v>471</v>
+        <v>569</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>472</v>
+        <v>570</v>
       </c>
       <c r="B27" t="s">
-        <v>473</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -6997,13 +8715,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>474</v>
+        <v>572</v>
       </c>
       <c r="B1" t="s">
-        <v>475</v>
+        <v>573</v>
       </c>
       <c r="C1" t="s">
-        <v>476</v>
+        <v>574</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -7011,13 +8729,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>477</v>
+        <v>575</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>576</v>
       </c>
       <c r="C2" t="s">
-        <v>479</v>
+        <v>577</v>
       </c>
       <c r="D2" t="n">
         <v>31500000</v>
@@ -7025,13 +8743,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>480</v>
+        <v>578</v>
       </c>
       <c r="B3" t="s">
-        <v>481</v>
+        <v>579</v>
       </c>
       <c r="C3" t="s">
-        <v>482</v>
+        <v>580</v>
       </c>
       <c r="D3" t="n">
         <v>90000000</v>
@@ -7059,35 +8777,35 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>483</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>484</v>
+        <v>582</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" t="n">
         <v>150000</v>
       </c>
       <c r="D2" t="s">
-        <v>485</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>486</v>
+        <v>584</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>45000</v>
       </c>
       <c r="D3" t="s">
-        <v>487</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
